--- a/workspaces/btc_daily_14days/drawdown/drawdown_7.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_7.xlsx
@@ -575,46 +575,46 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-12.49343832020543</v>
+        <v>-12.45441629321988</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.106007818435778</v>
+        <v>-4.093061309990212</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-14.50686598194545</v>
+        <v>-14.46146125779899</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.634595114915165</v>
+        <v>5.616297085906872</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.096996534881271</v>
+        <v>5.080599449252929</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.616372709704109</v>
+        <v>-4.601381304221349</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.702424401160009</v>
+        <v>-4.687075952518192</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.171441420154402</v>
+        <v>-5.154880312354358</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-15.25348120765798</v>
+        <v>-15.2048003986944</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.10900554042571</v>
+        <v>-16.05793494127836</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.29370593924618</v>
+        <v>-6.273811203158445</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.2606306733488</v>
+        <v>-6.240998859742014</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-16.71301039393574</v>
+        <v>-16.66021236268397</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.434749331035164</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.493438320202394</v>
+        <v>-2.486087198368715</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.56473591298863</v>
+        <v>12.52468057946985</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>45.5224967989742</v>
+        <v>45.37704344709366</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>28.98509345607855</v>
+        <v>28.89241372647491</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.77021732817374</v>
+        <v>11.73251933100281</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>28.75778768536068</v>
+        <v>28.66662873035165</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.702452187966351</v>
+        <v>-4.687043534579992</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.52379905384455</v>
+        <v>11.48729451943486</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-21.93334695503167</v>
+        <v>-21.86321763991689</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-56.19746621390679</v>
+        <v>-56.01861908638913</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-39.70889895150386</v>
+        <v>-39.58258663280417</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.260695912557296</v>
+        <v>-6.240986998062084</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-23.39951005501779</v>
+        <v>-23.32522627980642</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.434828690229253</v>
+        <v>-6.414552417432176</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.00656167978718</v>
+        <v>9.974016444942322</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20.90013441822698</v>
+        <v>20.833231850034</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20.5103237730774</v>
+        <v>20.44399508957247</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20.64572729634535</v>
+        <v>20.57918981447728</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.85566345850435</v>
+        <v>13.81109887110625</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>14.15670205830568</v>
+        <v>14.11169906695196</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.815968570798283</v>
+        <v>7.791465580177238</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.61082903210984</v>
+        <v>13.56745929998424</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.234081448102323</v>
+        <v>-5.216925248410142</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-12.35115438615522</v>
+        <v>-12.31142434318129</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-12.55936809655536</v>
+        <v>-12.5191125559641</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.52772816712249</v>
+        <v>-12.48789022450521</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.683917712260602</v>
+        <v>-6.662636752821861</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.434938670002566</v>
+        <v>-6.41455241742176</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>39.17322834646049</v>
+        <v>39.04699863213202</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.90016994530502</v>
+        <v>20.8328055250633</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20.51039423510886</v>
+        <v>20.44360754836623</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.30633326604514</v>
+        <v>12.26605880436401</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.428811071230577</v>
+        <v>3.417350075792548</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.72730126386768</v>
+        <v>3.715407004723026</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11.98888472007742</v>
+        <v>11.95084118381403</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.52405632810569</v>
+        <v>11.4870739986542</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.4654421508414</v>
+        <v>11.42920583557862</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>18.96813411394966</v>
+        <v>18.90778076789481</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>27.12156007021132</v>
+        <v>27.03494232733657</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>27.16298846177725</v>
+        <v>27.07591887326413</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>26.74816715853832</v>
+        <v>26.66246728572774</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>27.00540814459342</v>
+        <v>26.91878091590874</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>13</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.352715525940368</v>
+        <v>1.347284754202967</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.9530866975064</v>
+        <v>-7.928114761205642</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6538553874191635</v>
+        <v>-0.6530195276926847</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.87239689432381</v>
+        <v>14.82362448786211</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>14.33705833131536</v>
+        <v>14.29046040727246</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>14.63825574198506</v>
+        <v>14.59121317307304</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>14.55690595164683</v>
+        <v>14.51037196918819</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.318563440808362</v>
+        <v>-1.314490008940325</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.380344857180113</v>
+        <v>-1.375510617742535</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.476828795156642</v>
+        <v>5.459472020687052</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.984449632698</v>
+        <v>12.9427421252612</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>20.73570478550872</v>
+        <v>20.66875832956015</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>20.31932310256006</v>
+        <v>20.25375984593732</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>12.85790044178464</v>
+        <v>12.81621681334462</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>18</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19.72878390201224</v>
+        <v>19.66397477885513</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.56481537359036</v>
+        <v>12.52372705234001</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.056394934558426</v>
+        <v>1.051714812530705</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.746770575800497</v>
+        <v>6.723860364449706</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>17.33159692308703</v>
+        <v>17.27497079801736</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>23.19603174358112</v>
+        <v>23.12099379273684</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>23.11683684821146</v>
+        <v>23.0423044417252</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>17.08949410760399</v>
+        <v>17.03415907654291</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>11.46567116894767</v>
+        <v>11.42906269926457</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.048613630247047</v>
+        <v>5.03250592113902</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>10.41421000136107</v>
+        <v>10.38048068132397</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.6899203623346963</v>
+        <v>-0.6881987142669317</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.111609859032136</v>
+        <v>-1.108477222068906</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8612916997393185</v>
+        <v>-0.8589968618690449</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>26</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.198869372097711</v>
+        <v>5.180569570804671</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.588247024182664</v>
+        <v>3.575880578534317</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.042301791099561</v>
+        <v>7.01811599044381</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.174499956873305</v>
+        <v>7.149947612712261</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.912677916323432</v>
+        <v>-4.897633035540252</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.616193847930006</v>
+        <v>-4.6016674830611</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.702291226386919</v>
+        <v>-4.687231323098459</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-12.87714967990853</v>
+        <v>-12.83570180400032</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.380285754233611</v>
+        <v>-1.375547557083223</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-13.79708532942942</v>
+        <v>-13.75212170171933</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-21.71711496038563</v>
+        <v>-21.64678849681651</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-21.68785163808796</v>
+        <v>-21.61786777524203</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-22.11482224467444</v>
+        <v>-22.04339470845441</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-29.58715462995916</v>
+        <v>-29.49147549434768</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>23</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3195252767317172</v>
+        <v>-0.3200120430294291</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-10.62936303669587</v>
+        <v>-10.5954073865549</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.676926231201115</v>
+        <v>-6.656564669505983</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.505168543048121</v>
+        <v>6.482501600828179</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>14.67218056208294</v>
+        <v>14.62339190978767</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.266985181135937</v>
+        <v>6.246115635647946</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.183611640413702</v>
+        <v>6.163273303314291</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>14.42816106851829</v>
+        <v>14.38086413833802</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>10.01383581199658</v>
+        <v>9.981387333586774</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.164191788791953</v>
+        <v>9.134653685351111</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>13.32015102981653</v>
+        <v>13.27681431482043</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2785301742509461</v>
+        <v>0.2775726857569438</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1429833584337032</v>
+        <v>-0.1424972243356351</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.254690711391284</v>
+        <v>-4.240639373944369</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>33</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.0388928656659</v>
+        <v>-7.017238526551139</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.652614334524216</v>
+        <v>-8.624692207894583</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-6.017874976754911</v>
+        <v>-5.999396634851472</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.856291673900067</v>
+        <v>-2.848423719047723</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3626174069582007</v>
+        <v>-0.3625419088838626</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-12.20163720989373</v>
+        <v>-12.16192780088715</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-9.254761207954751</v>
+        <v>-9.224501193084912</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.76070839699397</v>
+        <v>-12.71905840147383</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.7524321391247</v>
+        <v>-6.730077278646284</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.531862444378007</v>
+        <v>-1.526564196084045</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.77532253480269</v>
+        <v>-4.759629254795861</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-13.85838354021588</v>
+        <v>-13.81275729165935</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-14.28351035197673</v>
+        <v>-14.23640807324746</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-17.07712850042577</v>
+        <v>-17.02061302348659</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>24</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-14.99343832020809</v>
+        <v>-14.94508923919643</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.106031178005701</v>
+        <v>-4.092780995202297</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.835595815798989</v>
+        <v>3.821665521270425</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.136943599710008</v>
+        <v>8.108468803251967</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.429130173320516</v>
+        <v>3.416632096101559</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>12.07152561970099</v>
+        <v>12.03131470205756</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7.816619923114843</v>
+        <v>7.79070566914536</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9976047180222807</v>
+        <v>-0.9943593903795147</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-17.75994497151842</v>
+        <v>-17.70076054627769</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-18.61659547818309</v>
+        <v>-18.55456163560598</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-14.64917130616479</v>
+        <v>-14.60050492641498</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-18.79704583033815</v>
+        <v>-18.73437792210227</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-31.76189024131811</v>
+        <v>-31.6561390420677</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-27.33925557313675</v>
+        <v>-27.24788575075793</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>38</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.769719574526874</v>
+        <v>2.759355773104033</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.106047460709391</v>
+        <v>-4.092585602739163</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-9.767869667138228</v>
+        <v>-9.736467305040769</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-9.639847206873782</v>
+        <v>-9.609246051988507</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-12.81561711811896</v>
+        <v>-12.77391456834157</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.616388005336375</v>
+        <v>-4.601356831214332</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.702538604655345</v>
+        <v>-4.686942715116551</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1008393086478137</v>
+        <v>0.1004580103167285</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-7.871728034799752</v>
+        <v>-7.844711921203093</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-11.36362404280256</v>
+        <v>-11.32488812150651</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-11.57166613037239</v>
+        <v>-11.5325284089779</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.81860241768528</v>
+        <v>-16.76155902105495</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-11.96541250742802</v>
+        <v>-11.92426657252118</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-11.71822788545644</v>
+        <v>-11.67771031216265</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>49</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-9.636295463067121</v>
+        <v>-9.604818266637942</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9973012757407886</v>
+        <v>0.9937601720811102</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.523014691363755</v>
+        <v>-5.505296417236963</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.478764338854297</v>
+        <v>-9.448014938942642</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1944461933443549</v>
+        <v>0.1929703707722368</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4921855272587479</v>
+        <v>0.4902316390850814</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.636678339583604</v>
+        <v>-1.631126629811028</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.194218411673809</v>
+        <v>-6.173258051407018</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.012942577452655</v>
+        <v>5.993480653980853</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.070979133129804</v>
+        <v>1.068421076825558</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.180039804772029</v>
+        <v>-1.175257982275653</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.9003249967670186</v>
+        <v>0.8985676417981097</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.568526267064144</v>
+        <v>-1.561708488899747</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.318677720369088</v>
+        <v>-1.312511601096212</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>44</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.052016225244564</v>
+        <v>2.044163605712434</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.71390201189331</v>
+        <v>2.70438436238662</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-9.049989671486927</v>
+        <v>-9.019735510782652</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.921911340726822</v>
+        <v>-8.892317758917045</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-11.7383626127118</v>
+        <v>-11.69893337775418</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-11.44376946034172</v>
+        <v>-11.40481923047795</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.08448063144626</v>
+        <v>-16.0292224717414</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-12.00300053986886</v>
+        <v>-11.96159587208795</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.512537891271315</v>
+        <v>-7.486071789615472</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.81070271302297</v>
+        <v>-3.796574581738398</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.295672177698343</v>
+        <v>-6.273221331622651</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.983948107415017</v>
+        <v>-3.968990731232147</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.406983851585991</v>
+        <v>-4.390260029090797</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.157883881860805</v>
+        <v>-4.141825144698366</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>45</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.050570653133434</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-9.663123787727145</v>
+        <v>-9.629891900751396</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.056308449545099</v>
+        <v>1.052190480101956</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.187036537256027</v>
+        <v>1.182233085511406</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.800877860615856</v>
+        <v>-3.788072049768296</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.504229628583467</v>
+        <v>-3.491921345130045</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8612616666472732</v>
+        <v>0.8589940053982943</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3933838562231315</v>
+        <v>0.3927297682043616</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.559100594023548</v>
+        <v>2.551224864145816</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.520197068933328</v>
+        <v>-0.5171584594694778</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.95382349517557</v>
+        <v>-2.942442603044832</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.378059362324151</v>
+        <v>-7.350961320330285</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-10.03143852345869</v>
+        <v>-9.99478779633202</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-12.01382602517222</v>
+        <v>-11.97010797297915</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>58</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7693003891754913</v>
+        <v>-0.7676567567502346</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.381526259160744</v>
+        <v>-2.373046917901569</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.052097548341642</v>
+        <v>-1.048894539184971</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.647470980971072</v>
+        <v>-2.638884893321936</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.71674861078872</v>
+        <v>3.703398657769405</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4.015416912038383</v>
+        <v>4.001548404436164</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.931422561299684</v>
+        <v>3.918263510807819</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.736941386563352</v>
+        <v>1.731530483850086</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.05179457927732045</v>
+        <v>-0.05068212763629276</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.361051580822952</v>
+        <v>-4.344381911828542</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.296469954235562</v>
+        <v>-6.272981998661493</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.076369267534098</v>
+        <v>-1.070739178037208</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2309108732419531</v>
+        <v>0.2323918995372836</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.249112695530009</v>
+        <v>-1.24213862432272</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>68</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>7.800679326848844</v>
+        <v>7.771587017144739</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>6.190800096437094</v>
+        <v>6.16877312326119</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>11.68311993787826</v>
+        <v>11.64067500669002</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11.81678625187616</v>
+        <v>11.77369917839176</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.808819653383111</v>
+        <v>9.773115079681233</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.691346766413268</v>
+        <v>5.670973416339088</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.134811124075455</v>
+        <v>4.120462993518863</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7208782218406427</v>
+        <v>0.7189297423993324</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.133541103612046</v>
+        <v>2.126840068528359</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1928698688130197</v>
+        <v>-0.1905965469603714</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3984443399758035</v>
+        <v>-0.3953308594103646</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3644314844534762</v>
+        <v>-0.3611634181475836</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7867107161953371</v>
+        <v>-0.7815216495525661</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9390341394362025</v>
+        <v>0.938388759045985</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>72</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.048993875765532</v>
+        <v>-8.021128253073655</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-11.05255786207231</v>
+        <v>-11.01223856417726</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-11.45058505855651</v>
+        <v>-11.40989522533748</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-12.71337820253257</v>
+        <v>-12.66823630037748</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7418637967452</v>
+        <v>-0.7402981379226219</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-7.398696766466159</v>
+        <v>-7.371885035627358</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.094654464665446</v>
+        <v>-6.072066804365768</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.781432217278244</v>
+        <v>-3.7669516926047</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.843833710355405</v>
+        <v>-3.828885640061742</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.305407009541739</v>
+        <v>-3.291633053767072</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.083161202904101</v>
+        <v>-9.04808573517068</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.871987543739955</v>
+        <v>-4.852065287345134</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.295622463925866</v>
+        <v>-5.27369839388524</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.046937855612867</v>
+        <v>-5.025663528534764</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>82</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.485183239183513</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.993075734942494</v>
+        <v>1.986228732351108</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.061973849050197</v>
+        <v>-2.054709452149602</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.611838378812415</v>
+        <v>6.586461816006818</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.074929461535064</v>
+        <v>6.050982071598675</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2677372082054887</v>
+        <v>0.2669696563877864</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.847577275368096</v>
+        <v>3.833857050871401</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.38039012190216</v>
+        <v>3.36863690246102</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.319998459518061</v>
+        <v>3.308726028835153</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.690665700560494</v>
+        <v>3.678796539694183</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.708842075459984</v>
+        <v>4.693717075355991</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.744521306754464</v>
+        <v>4.729239582903062</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.547272882838939</v>
+        <v>5.529479478075004</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.350840931328982</v>
+        <v>3.341545143550725</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>105</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.697037870266215</v>
+        <v>3.681794145004432</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>12.56535819705102</v>
+        <v>12.51721317079348</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.597547403247709</v>
+        <v>3.583312742672611</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.822753590184973</v>
+        <v>1.814498993740038</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.052083662515351</v>
+        <v>6.026891507312925</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.25874263699864</v>
+        <v>8.227005569621774</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.313963770151943</v>
+        <v>5.293804514273013</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.938474243856206</v>
+        <v>2.927777009643073</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.741948495860463</v>
+        <v>5.720675084227764</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.025802910833086</v>
+        <v>2.019716329063307</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.641418289392064</v>
+        <v>5.621842004441618</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.766428376105587</v>
+        <v>3.754081313086964</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.389402898438753</v>
+        <v>2.382840497875016</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.508372862917199</v>
+        <v>5.490209487337516</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>112</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.970847394075534</v>
+        <v>1.961496058037014</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.999327618701734</v>
+        <v>-4.980366563989477</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.644725913660508</v>
+        <v>2.633354744930386</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8.138239772155863</v>
+        <v>8.104148228438667</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4504629303497154</v>
+        <v>0.4460143451623821</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.642226895890644</v>
+        <v>1.634859326823658</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.914905926630716</v>
+        <v>-2.903466553765575</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.384295471838037</v>
+        <v>-3.370393166020044</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.3415442459929</v>
+        <v>-4.323868142590037</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.51029811818114</v>
+        <v>-2.49863030354399</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.403495837326147</v>
+        <v>-5.380159948019994</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.683294837073305</v>
+        <v>-2.670644336464349</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.210525643762573</v>
+        <v>-2.199109901386343</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.064347481893989</v>
+        <v>-1.057409560281954</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>121</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.052016225244756</v>
+        <v>2.041630322314866</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.039516650995957</v>
+        <v>-2.031451187081224</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.834618555735972</v>
+        <v>5.809134115520934</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.485600733633284</v>
+        <v>3.468316924341643</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.4653419634633167</v>
+        <v>0.4604999208929854</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.7629325130024114</v>
+        <v>0.758672488204617</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.8179608444172</v>
+        <v>4.798094429007641</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.865982524446984</v>
+        <v>1.859086885063725</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.1195790766157</v>
+        <v>5.099227006281652</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.781266650530426</v>
+        <v>1.775956940797066</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.234072653498487</v>
+        <v>3.223227119845262</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.04790053571990427</v>
+        <v>-0.04526684869927777</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.3590606525222242</v>
+        <v>0.360641220913017</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2201496178764444</v>
+        <v>-0.2162053099865844</v>
       </c>
     </row>
     <row r="27">
@@ -1664,49 +1664,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.368438320209975</v>
+        <v>-4.402502948946641</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.731598779717181</v>
+        <v>-4.773499563118463</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.288165268592422</v>
+        <v>-2.303812047286463</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.164283698461695</v>
+        <v>-7.220663054964653</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-8.952826612824225</v>
+        <v>-9.025905922359613</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-7.063577839579381</v>
+        <v>-7.123781448300477</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.147894973822609</v>
+        <v>-7.210247214779521</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.11348777214608</v>
+        <v>-10.20480292427207</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.552173204695286</v>
+        <v>-9.637535017276555</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-11.0191200570459</v>
+        <v>-11.12126994590685</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8.718289210984395</v>
+        <v>-8.800580076755104</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.19416315048963</v>
+        <v>-11.29924993053378</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-9.731900483218446</v>
+        <v>-9.825250647884914</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-9.487832527089608</v>
+        <v>-9.579109379449918</v>
       </c>
     </row>
     <row r="28">
@@ -1716,49 +1716,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.069876001015487</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.205994743368386</v>
+        <v>3.212792945376926</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.641213354792349</v>
+        <v>1.645956192126924</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5685142877676839</v>
+        <v>-0.5686941783665631</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.893823383087238</v>
+        <v>3.903402746107801</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.660528793910999</v>
+        <v>-1.664466074474333</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.330085951053029</v>
+        <v>-2.335940469493536</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.037172323312703</v>
+        <v>-1.041132248705622</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5132858181705515</v>
+        <v>-0.5157218197034723</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.9855041649456737</v>
+        <v>0.9853020033064439</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1949735030991562</v>
+        <v>0.1930808204721188</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9433243319392659</v>
+        <v>-0.9483251857145945</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.743726159770262</v>
+        <v>2.746978392338917</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.819596547515111</v>
+        <v>1.820741700222328</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-2.495946696350089</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.630243888594265</v>
+        <v>-3.634973984141766</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.215092875536811</v>
+        <v>1.217380060752717</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.08360272783212253</v>
+        <v>-0.08308647648336631</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.098943524641648</v>
+        <v>-1.099639542085015</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.278393446019045</v>
+        <v>-1.280255638384219</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.271018556323156</v>
+        <v>-3.275728908406371</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.787126965332504</v>
+        <v>-2.791745427975506</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.803506083917419</v>
+        <v>-3.8091949254338</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.794605613989752</v>
+        <v>-1.798302818857685</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.955983336275409</v>
+        <v>-2.961168223211786</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.924007816160866</v>
+        <v>-2.929545374452182</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.824737782375443</v>
+        <v>-3.831243252031449</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.342896708071919</v>
+        <v>-2.347566771491586</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.344125131566678</v>
+        <v>3.371330065353739</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.764440108264012</v>
+        <v>3.78938169876065</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.908981372476411</v>
+        <v>5.957247371536702</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.804858175435754</v>
+        <v>5.850980046253071</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.776789215015654</v>
+        <v>5.822680175291104</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.060922409787985</v>
+        <v>5.095749743237199</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.244051375814799</v>
+        <v>4.269992242306706</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.738266525796007</v>
+        <v>0.7356660386239184</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.848137247850353</v>
+        <v>-0.8614591535196467</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.688965769083858</v>
+        <v>-1.710864701414934</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.383927065035799</v>
+        <v>-1.404250246371255</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.348461608219878</v>
+        <v>-1.37092175060809</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.804023461879389</v>
+        <v>-3.843760929188065</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.007194726974887544</v>
+        <v>-0.004296007168072435</v>
       </c>
     </row>
     <row r="31">
@@ -1872,49 +1872,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.051059138053752</v>
+        <v>-3.053156256645828</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.602527129334241</v>
+        <v>-2.604897814872658</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.629074865619494</v>
+        <v>-2.63029843184966</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.985499104087666</v>
+        <v>-3.98811921155923</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.265390145651963</v>
+        <v>-5.269153910161435</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.619887227065526</v>
+        <v>-1.621232526710394</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.587198973096605</v>
+        <v>-0.5880721575993704</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8086531298567081</v>
+        <v>0.8083725745956514</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.857002757332779</v>
+        <v>-1.859657784195946</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.21648685173097</v>
+        <v>-1.218956367702837</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.422047289446333</v>
+        <v>-1.424762929608505</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.87918149109796</v>
+        <v>-2.883506413164255</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.437254260583124</v>
+        <v>-1.440393152685886</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.543317958201719</v>
+        <v>-4.548880775633648</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>350</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.363704536932815</v>
+        <v>2.354353166672595</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.9621547903171503</v>
+        <v>-0.9575284962270274</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.071309211199328</v>
+        <v>-1.071333449394992</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.630372492836614</v>
+        <v>1.62258700147747</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.225547600601573</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.389393215480112</v>
+        <v>3.378185565295844</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.876088069636566</v>
+        <v>3.864702977567411</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.410174300519834</v>
+        <v>3.402556522530489</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.922062992449284</v>
+        <v>3.91387408340519</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2091756425825793</v>
+        <v>0.2149549852783679</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2836099387992519</v>
+        <v>-0.2757984747524986</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2520854368615204</v>
+        <v>-0.2424058791348997</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.535240990629774</v>
+        <v>-1.521416606843808</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.431299889183911</v>
+        <v>-2.414552417424474</v>
       </c>
     </row>
     <row r="33">
@@ -1976,49 +1976,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.899942385250625</v>
+        <v>-2.89824853951486</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.343494317998079</v>
+        <v>-2.340889968980697</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-7.074406385028304</v>
+        <v>-7.069228650191867</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.692120732095574</v>
+        <v>-3.689898394845891</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.146531107059339</v>
+        <v>-3.144707983354309</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.9520701991539724</v>
+        <v>-0.9517391311100027</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.578809336480489</v>
+        <v>-1.577570676224816</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.539536494228976</v>
+        <v>-0.5384487270259726</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.840072542634587</v>
+        <v>1.83937286023729</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.80735489945706</v>
+        <v>1.807737443930236</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.874113426780127</v>
+        <v>1.87463255776305</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.63618991237788</v>
+        <v>1.63751162956649</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.66208529836414</v>
+        <v>3.661813206820817</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.095982563137888</v>
+        <v>3.096317147792725</v>
       </c>
     </row>
     <row r="34">
@@ -2028,7 +2028,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="inlineStr"/>
@@ -2185,10 +2185,8 @@
           <t>X &gt; -0.1871</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>4088~4101</t>
-        </is>
+      <c r="B6" t="n">
+        <v>4088</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-0.2135065962402081</v>
@@ -2239,10 +2237,8 @@
           <t>X &gt; -0.1806</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>4078~4091</t>
-        </is>
+      <c r="B7" t="n">
+        <v>4078</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-0.1834896524025922</v>
@@ -2293,10 +2289,8 @@
           <t>X &gt; -0.1742</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>4072~4085</t>
-        </is>
+      <c r="B8" t="n">
+        <v>4072</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-0.1800968269419272</v>
@@ -2347,10 +2341,8 @@
           <t>X &gt; -0.1677</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4056~4069</t>
-        </is>
+      <c r="B9" t="n">
+        <v>4056</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-0.2201525005982745</v>
@@ -2401,10 +2393,8 @@
           <t>X &gt; -0.1613</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>4044~4057</t>
-        </is>
+      <c r="B10" t="n">
+        <v>4044</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-0.3366722368971864</v>
@@ -2455,10 +2445,8 @@
           <t>X &gt; -0.1548</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>4031~4044</t>
-        </is>
+      <c r="B11" t="n">
+        <v>4031</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-0.3421030086372738</v>
@@ -2509,10 +2497,8 @@
           <t>X &gt; -0.1484</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>4013~4026</t>
-        </is>
+      <c r="B12" t="n">
+        <v>4013</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-0.4318387176267677</v>
@@ -2563,10 +2549,8 @@
           <t>X &gt; -0.1419</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3987~4000</t>
-        </is>
+      <c r="B13" t="n">
+        <v>3987</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.4684383202099767</v>
@@ -2617,10 +2601,8 @@
           <t>X &gt; -0.1355</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3964~3977</t>
-        </is>
+      <c r="B14" t="n">
+        <v>3964</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.4692995221209628</v>
@@ -2671,10 +2653,8 @@
           <t>X &gt; -0.129</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>3931~3944</t>
-        </is>
+      <c r="B15" t="n">
+        <v>3931</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-0.4143308151389746</v>
@@ -2725,10 +2705,8 @@
           <t>X &gt; -0.1226</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3907~3920</t>
-        </is>
+      <c r="B16" t="n">
+        <v>3907</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.3250709732712025</v>
@@ -2779,10 +2757,8 @@
           <t>X &gt; -0.1161</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>3869~3882</t>
-        </is>
+      <c r="B17" t="n">
+        <v>3869</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.3553651620440803</v>
@@ -2833,10 +2809,8 @@
           <t>X &gt; -0.1097</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>3820~3833</t>
-        </is>
+      <c r="B18" t="n">
+        <v>3820</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.2367203447338468</v>
@@ -2887,10 +2861,8 @@
           <t>X &gt; -0.1032</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>3776~3789</t>
-        </is>
+      <c r="B19" t="n">
+        <v>3776</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.2632984416140403</v>
@@ -2941,10 +2913,8 @@
           <t>X &gt; -0.09677</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>3731~3744</t>
-        </is>
+      <c r="B20" t="n">
+        <v>3731</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.3032673800390313</v>
@@ -2995,10 +2965,8 @@
           <t>X &gt; -0.09032</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3673~3686</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3673</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.2959342507579947</v>
@@ -3049,10 +3017,8 @@
           <t>X &gt; -0.08387</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3605~3618</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3605</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.4481094092094224</v>
@@ -3103,10 +3069,8 @@
           <t>X &gt; -0.07742</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3533~3546</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3533</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.2937767296854403</v>
@@ -3157,10 +3121,8 @@
           <t>X &gt; -0.07097</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3451~3464</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3451</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.2417062185933432</v>
@@ -3211,10 +3173,8 @@
           <t>X &gt; -0.06452</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3346~3359</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3346</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.3648286149405493</v>
@@ -3265,10 +3225,8 @@
           <t>X &gt; -0.05806</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3234~3247</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3234</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.4453939715804651</v>
@@ -3319,10 +3277,8 @@
           <t>X &gt; -0.05161</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3113~3126</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3113</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.5420627603891219</v>
@@ -3373,10 +3329,8 @@
           <t>X &gt; -0.04516</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2955~2966</t>
-        </is>
+      <c r="B28" t="n">
+        <v>2955</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>-0.3356500531836772</v>
@@ -3427,10 +3381,8 @@
           <t>X &gt; -0.03871</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2785~2795</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2785</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-0.5435277656482569</v>
@@ -3481,10 +3433,8 @@
           <t>X &gt; -0.03226</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2576~2585</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2576</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-0.3851211055097821</v>
@@ -3535,10 +3485,8 @@
           <t>X &gt; -0.02581</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2381~2388</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2381</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.6927683034595589</v>
@@ -3589,10 +3537,8 @@
           <t>X &gt; -0.01935</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2113~2119</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2113</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-0.3933911281382478</v>
@@ -3643,10 +3589,8 @@
           <t>X &gt; -0.0129</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>1763~1769</t>
-        </is>
+      <c r="B33" t="n">
+        <v>1763</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.9388877266542934</v>
@@ -3697,10 +3641,8 @@
           <t>X &gt; -0.006452</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1395~1400</t>
-        </is>
+      <c r="B34" t="n">
+        <v>1395</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.4220097487814058</v>
@@ -3751,10 +3693,8 @@
           <t>X &gt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>0~0</t>
-        </is>
+      <c r="B35" t="n">
+        <v>0</v>
       </c>
       <c r="C35" s="4" t="inlineStr"/>
       <c r="D35" s="4" t="inlineStr"/>
@@ -3911,10 +3851,8 @@
           <t>X &lt; -0.1871</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>84~84</t>
-        </is>
+      <c r="B6" t="n">
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>9.41132358455193</v>
@@ -3965,10 +3903,8 @@
           <t>X &lt; -0.1806</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>94~94</t>
-        </is>
+      <c r="B7" t="n">
+        <v>94</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>7.081029764896407</v>
@@ -4019,10 +3955,8 @@
           <t>X &lt; -0.1742</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>100~100</t>
-        </is>
+      <c r="B8" t="n">
+        <v>100</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>6.506561679790025</v>
@@ -4073,10 +4007,8 @@
           <t>X &lt; -0.1677</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>116~116</t>
-        </is>
+      <c r="B9" t="n">
+        <v>116</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>6.989320300479683</v>
@@ -4127,10 +4059,8 @@
           <t>X &lt; -0.1613</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>128~128</t>
-        </is>
+      <c r="B10" t="n">
+        <v>128</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>10.00656167979002</v>
@@ -4181,10 +4111,8 @@
           <t>X &lt; -0.1548</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>141~141</t>
-        </is>
+      <c r="B11" t="n">
+        <v>141</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>9.20868933936449</v>
@@ -4235,10 +4163,8 @@
           <t>X &lt; -0.1484</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>159~159</t>
-        </is>
+      <c r="B12" t="n">
+        <v>159</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>10.39964344079631</v>
@@ -4289,10 +4215,8 @@
           <t>X &lt; -0.1419</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>185~185</t>
-        </is>
+      <c r="B13" t="n">
+        <v>185</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>9.668723841952186</v>
@@ -4343,10 +4267,8 @@
           <t>X &lt; -0.1355</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>208~208</t>
-        </is>
+      <c r="B14" t="n">
+        <v>208</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>8.564253987482338</v>
@@ -4397,10 +4319,8 @@
           <t>X &lt; -0.129</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>241~241</t>
-        </is>
+      <c r="B15" t="n">
+        <v>241</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>6.42772350551617</v>
@@ -4451,10 +4371,8 @@
           <t>X &lt; -0.1226</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>265~265</t>
-        </is>
+      <c r="B16" t="n">
+        <v>265</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>4.487693755261724</v>
@@ -4505,10 +4423,8 @@
           <t>X &lt; -0.1161</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>303~303</t>
-        </is>
+      <c r="B17" t="n">
+        <v>303</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>4.272238247446786</v>
@@ -4559,10 +4475,8 @@
           <t>X &lt; -0.1097</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>352~352</t>
-        </is>
+      <c r="B18" t="n">
+        <v>352</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>2.336107134335485</v>
@@ -4613,10 +4527,8 @@
           <t>X &lt; -0.1032</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>396~396</t>
-        </is>
+      <c r="B19" t="n">
+        <v>396</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>2.304541477769824</v>
@@ -4667,10 +4579,8 @@
           <t>X &lt; -0.09677</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>441~441</t>
-        </is>
+      <c r="B20" t="n">
+        <v>441</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>2.381845126502043</v>
@@ -4721,10 +4631,8 @@
           <t>X &lt; -0.09032</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>499~499</t>
-        </is>
+      <c r="B21" t="n">
+        <v>499</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>2.015579715862167</v>
@@ -4775,10 +4683,8 @@
           <t>X &lt; -0.08387</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>567~567</t>
-        </is>
+      <c r="B22" t="n">
+        <v>567</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.709383549278563</v>
@@ -4829,10 +4735,8 @@
           <t>X &lt; -0.07742</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>639~639</t>
-        </is>
+      <c r="B23" t="n">
+        <v>639</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.497172008428521</v>
@@ -4883,10 +4787,8 @@
           <t>X &lt; -0.07097</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>721~721</t>
-        </is>
+      <c r="B24" t="n">
+        <v>721</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.04331618741832</v>
@@ -4937,10 +4839,8 @@
           <t>X &lt; -0.06452</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>826~826</t>
-        </is>
+      <c r="B25" t="n">
+        <v>826</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>1.380653689475253</v>
@@ -4991,10 +4891,8 @@
           <t>X &lt; -0.05806</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>938~938</t>
-        </is>
+      <c r="B26" t="n">
+        <v>938</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>1.451124579576813</v>
@@ -5045,10 +4943,8 @@
           <t>X &lt; -0.05161</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1059~1059</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1059</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.519781698675772</v>
@@ -5099,10 +4995,8 @@
           <t>X &lt; -0.04516</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1217~1219</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1217</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.7469226313897011</v>
@@ -5153,10 +5047,8 @@
           <t>X &lt; -0.03871</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>1387~1390</t>
-        </is>
+      <c r="B29" t="n">
+        <v>1387</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.031741535905141</v>
@@ -5207,10 +5099,8 @@
           <t>X &lt; -0.03226</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>1596~1600</t>
-        </is>
+      <c r="B30" t="n">
+        <v>1596</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.5690616797900248</v>
@@ -5261,10 +5151,8 @@
           <t>X &lt; -0.02581</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>1791~1797</t>
-        </is>
+      <c r="B31" t="n">
+        <v>1791</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.8732839947594186</v>
@@ -5315,10 +5203,8 @@
           <t>X &lt; -0.01935</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2059~2066</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2059</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.3623216023456948</v>
@@ -5369,10 +5255,8 @@
           <t>X &lt; -0.0129</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2409~2416</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2409</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.6522570440284312</v>
@@ -5423,10 +5307,8 @@
           <t>X &lt; -0.006452</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2777~2785</t>
-        </is>
+      <c r="B34" t="n">
+        <v>2777</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1816065630934389</v>
@@ -5477,10 +5359,8 @@
           <t>X &lt; 0</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3157~3166</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3157</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-0.1876897415618402</v>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_7.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_7.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-7 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-7 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,46 +575,46 @@
         <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-12.45441629321988</v>
+        <v>-12.44194402965459</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.093061309990212</v>
+        <v>-4.080193097827816</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-14.46146125779899</v>
+        <v>-14.44849912705146</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.616297085906872</v>
+        <v>5.629247305796291</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.080599449252929</v>
+        <v>5.093683566152031</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.601381304221349</v>
+        <v>-4.588366804943632</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.687075952518192</v>
+        <v>-4.674034650773294</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.154880312354358</v>
+        <v>-5.14172097423512</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-15.2048003986944</v>
+        <v>-15.19162277836122</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.05793494127836</v>
+        <v>-16.04454707469355</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.273811203158445</v>
+        <v>-6.260365135987072</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.240998859742014</v>
+        <v>-6.2275540388829</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-16.66021236268397</v>
+        <v>-16.64666070157931</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>-6.4249820531182</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>6</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.486087198368715</v>
+        <v>-2.473607379632448</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.52468057946985</v>
+        <v>12.53756060542122</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>45.37704344709366</v>
+        <v>45.39004494495706</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>28.89241372647491</v>
+        <v>28.90537784643106</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.73251933100281</v>
+        <v>11.74560695593512</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>28.66662873035165</v>
+        <v>28.67965912498195</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.687043534579992</v>
+        <v>-4.674002338639646</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.48729451943486</v>
+        <v>11.50045977693366</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-21.86321763991689</v>
+        <v>-21.85004212535651</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-56.01861908638913</v>
+        <v>-56.00524093089307</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-39.58258663280417</v>
+        <v>-39.56914663471216</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.240986998062084</v>
+        <v>-6.227542209436976</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-23.32522627980642</v>
+        <v>-23.31167504161225</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.414552417432176</v>
+        <v>-6.424982053137917</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.974016444942322</v>
+        <v>9.986505836668336</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20.833231850034</v>
+        <v>20.84611780539439</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20.44399508957247</v>
+        <v>20.45698009883601</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20.57918981447728</v>
+        <v>20.59214890863108</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.81109887110625</v>
+        <v>13.82418753976997</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>14.11169906695196</v>
+        <v>14.12472240655228</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.791465580177238</v>
+        <v>7.804511928597393</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.56745929998424</v>
+        <v>13.58062525204615</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.216925248410142</v>
+        <v>-5.203744843805595</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-12.31142434318129</v>
+        <v>-12.29803579321239</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-12.5191125559641</v>
+        <v>-12.5056677601407</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.48789022450521</v>
+        <v>-12.47444623946888</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.662636752821861</v>
+        <v>-6.649084535971596</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.41455241742176</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>39.04699863213202</v>
+        <v>39.05951088322954</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.8328055250633</v>
+        <v>20.84569142087074</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20.44360754836623</v>
+        <v>20.45659250046328</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.26605880436401</v>
+        <v>12.27901277800483</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.417350075792548</v>
+        <v>3.430432938424943</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.715407004723026</v>
+        <v>3.728425182179215</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11.95084118381403</v>
+        <v>11.96388919403732</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.4870739986542</v>
+        <v>11.50023911891025</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.42920583557862</v>
+        <v>11.44239118393679</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>18.90778076789481</v>
+        <v>18.92117680876711</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>27.03494232733657</v>
+        <v>27.04839426952692</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>27.07591887326413</v>
+        <v>27.08936762522463</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>26.66246728572774</v>
+        <v>26.67602151000521</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>26.91878091590874</v>
+        <v>26.90835128021059</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>13</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.347284754202967</v>
+        <v>1.359767079485053</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.928114761205642</v>
+        <v>-7.915250089778183</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6530195276926847</v>
+        <v>-0.6400488653755332</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.82362448786211</v>
+        <v>14.83657992307786</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>14.29046040727246</v>
+        <v>14.30354911673293</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>14.59121317307304</v>
+        <v>14.60423655145368</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>14.51037196918819</v>
+        <v>14.52342099841111</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.314490008940325</v>
+        <v>-1.30132967968315</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.375510617742535</v>
+        <v>-1.362329265199207</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.459472020687052</v>
+        <v>5.472864727353254</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.9427421252612</v>
+        <v>12.95619146579706</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>20.66875832956015</v>
+        <v>20.68220629215329</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>20.25375984593732</v>
+        <v>20.2673136748604</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>12.81621681334462</v>
+        <v>12.80578717764647</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>18</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19.66397477885513</v>
+        <v>19.67647154155095</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.52372705234001</v>
+        <v>12.53660652242841</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.051714812530705</v>
+        <v>1.064686353568796</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.723860364449706</v>
+        <v>6.736810673188167</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>17.27497079801736</v>
+        <v>17.2880610629425</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>23.12099379273684</v>
+        <v>23.13402130410978</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>23.0423044417252</v>
+        <v>23.05535708747624</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>17.03415907654291</v>
+        <v>17.04732606705104</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>11.42906269926457</v>
+        <v>11.44224788373431</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.03250592113902</v>
+        <v>5.045898436318495</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>10.38048068132397</v>
+        <v>10.39392950215377</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.6881987142669317</v>
+        <v>-0.6747534156199322</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.108477222068906</v>
+        <v>-1.094924726414938</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8589968618690449</v>
+        <v>-0.8694264975621451</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>26</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.180569570804671</v>
+        <v>5.193054428352639</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.575880578534317</v>
+        <v>3.588753086766296</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.01811599044381</v>
+        <v>7.031091267119059</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.149947612712261</v>
+        <v>7.162897920074428</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.897633035540252</v>
+        <v>-4.884555410619924</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.6016674830611</v>
+        <v>-4.588653934014701</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.687231323098459</v>
+        <v>-4.674190902821827</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-12.83570180400032</v>
+        <v>-12.82254615196832</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.375547557083223</v>
+        <v>-1.362366504583946</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-13.75212170171933</v>
+        <v>-13.73873403276353</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-21.64678849681651</v>
+        <v>-21.63334578615597</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-21.61786777524203</v>
+        <v>-21.60442518573198</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-22.04339470845441</v>
+        <v>-22.02984356895089</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-29.49147549434768</v>
+        <v>-29.50190513004758</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>23</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3200120430294291</v>
+        <v>-0.3075321244520737</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-10.5954073865549</v>
+        <v>-10.58254608944403</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.656564669505983</v>
+        <v>-6.643599265768565</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.482501600828179</v>
+        <v>6.495451187883475</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>14.62339190978767</v>
+        <v>14.63648024598769</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.246115635647946</v>
+        <v>6.259134305277193</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.163273303314291</v>
+        <v>6.176318203634139</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>14.38086413833802</v>
+        <v>14.39402979204501</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.981387333586774</v>
+        <v>9.994571770454613</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.134653685351111</v>
+        <v>9.14804691443473</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>13.27681431482043</v>
+        <v>13.29026345577071</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2775726857569438</v>
+        <v>0.2910179066750942</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1424972243356351</v>
+        <v>-0.1289447695034838</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.240639373944369</v>
+        <v>-4.251069009646471</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>33</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.017238526551139</v>
+        <v>-7.004764821884045</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.624692207894583</v>
+        <v>-8.611830187477857</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.999396634851472</v>
+        <v>-5.986431419612465</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.848423719047723</v>
+        <v>-2.835480510349477</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3625419088838626</v>
+        <v>-0.3494624758102702</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-12.16192780088715</v>
+        <v>-12.1489189373595</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-9.224501193084912</v>
+        <v>-9.21146351315393</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.71905840147383</v>
+        <v>-12.70590339082464</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.730077278646284</v>
+        <v>-6.716898399089857</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.526564196084045</v>
+        <v>-1.513173859586267</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.759629254795861</v>
+        <v>-4.746183691698697</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-13.81275729165935</v>
+        <v>-13.7993139930918</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-14.23640807324746</v>
+        <v>-14.2228565812898</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-17.02061302348659</v>
+        <v>-17.03104265918198</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>24</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-14.94508923919643</v>
+        <v>-14.93262304896543</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.092780995202297</v>
+        <v>-4.079916214752508</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.821665521270425</v>
+        <v>3.834637124224891</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.108468803251967</v>
+        <v>8.121418624446953</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.416632096101559</v>
+        <v>3.429713294964976</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>12.03131470205756</v>
+        <v>12.04433562939371</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7.79070566914536</v>
+        <v>7.803750659154652</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9943593903795147</v>
+        <v>-0.9812002296727513</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-17.70076054627769</v>
+        <v>-17.68758557604988</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-18.55456163560598</v>
+        <v>-18.54117597707231</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-14.60050492641498</v>
+        <v>-14.5870614798696</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-18.73437792210227</v>
+        <v>-18.72093542513097</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-31.6561390420677</v>
+        <v>-31.64258877063986</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-27.24788575075793</v>
+        <v>-27.25831538645609</v>
       </c>
     </row>
     <row r="16">
@@ -1092,49 +1092,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2.759355773104033</v>
+        <v>3.915090631901883</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-4.092585602739163</v>
+        <v>-5.357805598415567</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-9.736467305040769</v>
+        <v>-10.86734574899459</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-9.609246051988507</v>
+        <v>-10.74044366763142</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-12.77391456834157</v>
+        <v>-13.83795264419168</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.601356831214332</v>
+        <v>-5.867748475320937</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-4.686942715116551</v>
+        <v>-5.953637586753146</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1004580103167285</v>
+        <v>-1.301192775451241</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-7.844711921203093</v>
+        <v>-9.04453876243484</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-11.32488812150651</v>
+        <v>-12.45741165371955</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-11.5325284089779</v>
+        <v>-12.66529203841539</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-16.76155902105495</v>
+        <v>-17.75973700418957</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-11.92426657252118</v>
+        <v>-13.05751640074705</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-11.67771031216265</v>
+        <v>-12.83523846337916</v>
       </c>
     </row>
     <row r="17">
@@ -1144,49 +1144,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-9.604818266637942</v>
+        <v>-10.77883115691431</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.9937601720811102</v>
+        <v>2.151036094239259</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.505296417236963</v>
+        <v>-4.474814181578004</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-9.448014938942642</v>
+        <v>-8.502109413755129</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.1929703707722368</v>
+        <v>1.35134307137136</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.4902316390850814</v>
+        <v>1.648835580876515</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-1.631126629811028</v>
+        <v>-0.5146404255527131</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-6.173258051407018</v>
+        <v>-5.141271210436201</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>5.993480653980853</v>
+        <v>7.280524655651838</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.068421076825558</v>
+        <v>2.271057658310106</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.175257982275653</v>
+        <v>-0.01474238905721137</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.8985676417981097</v>
+        <v>2.101873394857869</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-1.561708488899747</v>
+        <v>-0.4004937517130287</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.312511601096212</v>
+        <v>-0.1749820531227542</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>44</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.044163605712434</v>
+        <v>2.056641215967325</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.70438436238662</v>
+        <v>2.717251835415283</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-9.019735510782652</v>
+        <v>-9.006776261862306</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.892317758917045</v>
+        <v>-8.87938189892806</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-11.69893337775418</v>
+        <v>-11.68586371052636</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-11.40481923047795</v>
+        <v>-11.39181276155786</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.0292224717414</v>
+        <v>-16.01619052258476</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-11.96159587208795</v>
+        <v>-11.94844280246271</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.486071789615472</v>
+        <v>-7.472894893891613</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.796574581738398</v>
+        <v>-3.783186197641179</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.273221331622651</v>
+        <v>-6.259777140267765</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.968990731232147</v>
+        <v>-3.955546889621843</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.390260029090797</v>
+        <v>-4.37670827986603</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.141825144698366</v>
+        <v>-4.152254780395481</v>
       </c>
     </row>
     <row r="19">
@@ -1251,46 +1251,46 @@
         <v>45</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.050570653133434</v>
+        <v>3.063048187955189</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-9.629891900751396</v>
+        <v>-9.617035973947424</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.052190480101956</v>
+        <v>1.065156360755765</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.182233085511406</v>
+        <v>1.19517498695361</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.788072049768296</v>
+        <v>-3.774998434292165</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.491921345130045</v>
+        <v>-3.478911359362272</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8589940053982943</v>
+        <v>0.8720334224018771</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3927297682043616</v>
+        <v>0.405887365678069</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.551224864145816</v>
+        <v>2.564404774145039</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5171584594694778</v>
+        <v>-0.5037695609229615</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.942442603044832</v>
+        <v>-2.928998039938193</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.350961320330285</v>
+        <v>-7.337518180267907</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-9.99478779633202</v>
+        <v>-9.981236560176626</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-11.97010797297915</v>
+        <v>-11.98053760867831</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>58</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7676567567502346</v>
+        <v>-0.7551840496930566</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.373046917901569</v>
+        <v>-2.360186298048525</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.048894539184971</v>
+        <v>-1.035931492589917</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.638884893321936</v>
+        <v>-2.625946828867939</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.703398657769405</v>
+        <v>3.716476149809054</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4.001548404436164</v>
+        <v>4.014561844577514</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.918263510807819</v>
+        <v>3.93130377006991</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.731530483850086</v>
+        <v>1.744688022638023</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.05068212763629276</v>
+        <v>-0.03750368444154617</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.344381911828542</v>
+        <v>-4.33099460810633</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.272981998661493</v>
+        <v>-6.259538552004187</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.070739178037208</v>
+        <v>-1.057295395852407</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2323918995372836</v>
+        <v>0.2459437370288811</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.24213862432272</v>
+        <v>-1.252568260019309</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>68</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>7.771587017144739</v>
+        <v>7.784066490859288</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>6.16877312326119</v>
+        <v>6.181639813254741</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>11.64067500669002</v>
+        <v>11.65364719635706</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11.77369917839176</v>
+        <v>11.78664680389813</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.773115079681233</v>
+        <v>9.786195691753825</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.670973416339088</v>
+        <v>5.683986937142279</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.120462993518863</v>
+        <v>4.133502523442694</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7189297423993324</v>
+        <v>0.7320860200231536</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.126840068528359</v>
+        <v>2.14001863576636</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1905965469603714</v>
+        <v>-0.1772086383002716</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3953308594103646</v>
+        <v>-0.3818865933925366</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3611634181475836</v>
+        <v>-0.3477198323140627</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7815216495525661</v>
+        <v>-0.7679700381612804</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.938388759045985</v>
+        <v>0.9279591233478328</v>
       </c>
     </row>
     <row r="22">
@@ -1407,202 +1407,202 @@
         <v>72</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.021128253073655</v>
+        <v>-8.008666527363296</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-11.01223856417726</v>
+        <v>-10.99938980625963</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-11.40989522533748</v>
+        <v>-11.39694425898359</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-12.66823630037748</v>
+        <v>-12.65530907013213</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7402981379226219</v>
+        <v>-0.7272260015467324</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-7.371885035627358</v>
+        <v>-7.358880873815487</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.072066804365768</v>
+        <v>-6.059033947674862</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.7669516926047</v>
+        <v>-3.753798535052454</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.828885640061742</v>
+        <v>-3.815710223606153</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.291633053767072</v>
+        <v>-3.278246826654595</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.04808573517068</v>
+        <v>-9.034644070148893</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.852065287345134</v>
+        <v>-4.838622770681688</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.27369839388524</v>
+        <v>-5.260147322299126</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.025663528534764</v>
+        <v>-5.036093164233868</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ -0.0742</t>
+          <t>X ≈ -0.07419</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>82</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.485183239183513</v>
+        <v>-2.472718545595733</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.986228732351108</v>
+        <v>1.999087344819721</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.054709452149602</v>
+        <v>-2.041752816248582</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.586461816006818</v>
+        <v>6.59940240572594</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.050982071598675</v>
+        <v>6.064057590815096</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2669696563877864</v>
+        <v>0.279976999343603</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.833857050871401</v>
+        <v>3.846894072687292</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.36863690246102</v>
+        <v>3.381792321065092</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.308726028835153</v>
+        <v>3.321903323550266</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.678796539694183</v>
+        <v>3.692184207636927</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.693717075355991</v>
+        <v>4.707161396791321</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.729239582903062</v>
+        <v>4.742683231905986</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.529479478075004</v>
+        <v>5.543031212587103</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.341545143550725</v>
+        <v>3.331115507853134</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.06774</t>
+          <t>X ≈ -0.06773</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>105</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.681794145004432</v>
+        <v>3.69426262678703</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>12.51721317079348</v>
+        <v>12.53008028204025</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.583312742672611</v>
+        <v>3.59627198394876</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.814498993740038</v>
+        <v>1.82743351253476</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.026891507312925</v>
+        <v>6.039965317183153</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.227005569621774</v>
+        <v>8.240016611441732</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.293804514273013</v>
+        <v>5.306840939993776</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.927777009643073</v>
+        <v>2.940930855673741</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.720675084227764</v>
+        <v>5.733852330154242</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.019716329063307</v>
+        <v>2.033102491717365</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.621842004441618</v>
+        <v>5.635285908385043</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.754081313086964</v>
+        <v>3.767524344856966</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.382840497875016</v>
+        <v>2.396391733510256</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.490209487337516</v>
+        <v>5.479779851638931</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ -0.06129</t>
+          <t>X ≈ -0.06128</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>112</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.961496058037014</v>
+        <v>1.973959130737136</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.980366563989477</v>
+        <v>-4.967521383636793</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.633354744930386</v>
+        <v>2.646310038234155</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8.104148228438667</v>
+        <v>8.117085887834897</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4460143451623821</v>
+        <v>0.4590812534481259</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.634859326823658</v>
+        <v>1.64786361285104</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.903466553765575</v>
+        <v>-2.890437372785314</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.370393166020044</v>
+        <v>-3.357244641823307</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.323868142590037</v>
+        <v>-4.310696959803167</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.49863030354399</v>
+        <v>-2.485247098066623</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.380159948019994</v>
+        <v>-5.366719999724381</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.670644336464349</v>
+        <v>-2.657203113325501</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.199109901386343</v>
+        <v>-2.185559415707672</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.057409560281954</v>
+        <v>-1.067839195980106</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>121</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.041630322314866</v>
+        <v>2.054089313470385</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.031451187081224</v>
+        <v>-2.018607606581639</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.809134115520934</v>
+        <v>5.822089365215597</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.468316924341643</v>
+        <v>3.481247351162708</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.4604999208929854</v>
+        <v>0.473563641411971</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.758672488204617</v>
+        <v>0.7716732801488746</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.798094429007641</v>
+        <v>4.811126243400466</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.859086885063725</v>
+        <v>1.872236059909717</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.099227006281652</v>
+        <v>5.112400819922833</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.775956940797066</v>
+        <v>1.789340183472433</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.223227119845262</v>
+        <v>3.236668302191887</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.04526684869927777</v>
+        <v>-0.03182595843330915</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.360641220913017</v>
+        <v>0.374191533530599</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2162053099865844</v>
+        <v>-0.2266349456843599</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>158</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.402502948946641</v>
+        <v>-4.38983757587679</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.773499563118463</v>
+        <v>-4.760435249495131</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.303812047286463</v>
+        <v>-2.63178029000413</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.220663054964653</v>
+        <v>-7.207634358426596</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-9.025905922359613</v>
+        <v>-9.012740020579635</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-7.123781448300477</v>
+        <v>-7.455897733083873</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.210247214779521</v>
+        <v>-7.197227902881565</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.20480292427207</v>
+        <v>-10.19166491638425</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.637535017276555</v>
+        <v>-9.624371723864677</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-11.12126994590685</v>
+        <v>-11.10789461195679</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8.800580076755104</v>
+        <v>-8.787144459015423</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.29924993053378</v>
+        <v>-11.28581270332813</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-9.825250647884914</v>
+        <v>-9.811702045850055</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-9.579109379449918</v>
+        <v>-9.589539015148212</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>170</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.069876001015487</v>
+        <v>3.082442828894628</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.212792945376926</v>
+        <v>3.225754628739644</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.645956192126924</v>
+        <v>1.659710812193502</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5686941783665631</v>
+        <v>-0.5556605606809697</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.903402746107801</v>
+        <v>3.59767370168619</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.664466074474333</v>
+        <v>-1.65204370811221</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.335940469493536</v>
+        <v>-2.322922989714023</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.041132248705622</v>
+        <v>-1.027993107916721</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5157218197034723</v>
+        <v>-0.5025575149105421</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.9853020033064439</v>
+        <v>0.9986794054942507</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.1930808204721188</v>
+        <v>0.2065169628394088</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9483251857145945</v>
+        <v>-0.9348874047557558</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.746978392338917</v>
+        <v>2.760527586728379</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.820741700222328</v>
+        <v>1.810312064524176</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.495946696350089</v>
+        <v>-2.237394607640489</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.634973984141766</v>
+        <v>-3.369284734427566</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.217380060752717</v>
+        <v>1.431142519321966</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.08308647648336631</v>
+        <v>0.1437485779513636</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.099639542085015</v>
+        <v>-0.8656296774909933</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.280255638384219</v>
+        <v>-1.03973962466528</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.275728908406371</v>
+        <v>-3.014268564545816</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.791745427975506</v>
+        <v>-2.534945889925176</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.8091949254338</v>
+        <v>-3.543488441672089</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.798302818857685</v>
+        <v>-1.553794692644338</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.961168223211786</v>
+        <v>-2.706046347044257</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.929545374452182</v>
+        <v>-2.672921667137437</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.831243252031449</v>
+        <v>-3.568287459891671</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.347566771491586</v>
+        <v>-1.922612384876089</v>
       </c>
     </row>
     <row r="30">
@@ -1820,49 +1820,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.371330065353739</v>
+        <v>2.889745645576944</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.78938169876065</v>
+        <v>3.584775289543934</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.957247371536702</v>
+        <v>5.767162958909353</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.850980046253071</v>
+        <v>5.382919059716542</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.822680175291104</v>
+        <v>5.63400938146026</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>5.095749743237199</v>
+        <v>4.901723738080179</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>4.269992242306706</v>
+        <v>3.78745548995785</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.7356660386239184</v>
+        <v>0.5221387105810678</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.8614591535196467</v>
+        <v>-1.082340699720966</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.710864701414934</v>
+        <v>-1.93112521186908</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.404250246371255</v>
+        <v>-1.62199154747244</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.37092175060809</v>
+        <v>-1.588624988229661</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-3.843760929188065</v>
+        <v>-4.071008815152481</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.004296007168072435</v>
+        <v>-0.2394150428135973</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>268</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.053156256645828</v>
+        <v>-3.040633966970205</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.604897814872658</v>
+        <v>-2.793516464643382</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.63029843184966</v>
+        <v>-2.617291300432058</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.98811921155923</v>
+        <v>-3.975140069160766</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.269153910161435</v>
+        <v>-5.256043105786496</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.621232526710394</v>
+        <v>-1.608189630416028</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5880721575993704</v>
+        <v>-0.5750059032988943</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8083725745956514</v>
+        <v>0.8216358362421303</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.859657784195946</v>
+        <v>-1.845103877166601</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.218956367702837</v>
+        <v>-1.204283939906091</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.424762929608505</v>
+        <v>-1.40989557715843</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.883506413164255</v>
+        <v>-2.867775638875791</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.440393152685886</v>
+        <v>-1.425177561748946</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.548880775633648</v>
+        <v>-4.559310411331801</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>350</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.354353166672595</v>
+        <v>2.366875456348218</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.9575284962270274</v>
+        <v>-0.9446186866509763</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.071333449394992</v>
+        <v>-1.058326317977389</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.62258700147747</v>
+        <v>1.635566143875934</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.225547600601573</v>
+        <v>2.238658404976512</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.378185565295844</v>
+        <v>3.39122846159021</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.864702977567411</v>
+        <v>3.877769231867887</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.402556522530489</v>
+        <v>3.414382049866909</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.91387408340519</v>
+        <v>3.925636113739088</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2149549852783679</v>
+        <v>0.229259150559912</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2757984747524986</v>
+        <v>-0.2610882843373332</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.2424058791348997</v>
+        <v>-0.227373686406338</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.521416606843808</v>
+        <v>-1.505573679167576</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.414552417424474</v>
+        <v>-2.424982053122626</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>368</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.89824853951486</v>
+        <v>-2.885726249839237</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.340889968980697</v>
+        <v>-2.327980159404646</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-7.069228650191867</v>
+        <v>-7.056221518774265</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.689898394845891</v>
+        <v>-3.676919252447426</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.144707983354309</v>
+        <v>-3.131597178979369</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.9517391311100027</v>
+        <v>-0.9386962348156374</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.577570676224816</v>
+        <v>-1.56450442192434</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.5384487270259726</v>
+        <v>-0.6766068866226504</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.83937286023729</v>
+        <v>1.851879850880707</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.807737443930236</v>
+        <v>1.821364501677046</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.87463255776305</v>
+        <v>1.888448004831744</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.63751162956649</v>
+        <v>1.65201014553724</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.661813206820817</v>
+        <v>3.675119423162776</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.096317147792725</v>
+        <v>3.085887512094573</v>
       </c>
     </row>
     <row r="34">
@@ -2093,7 +2093,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-7 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-7 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2186,49 +2186,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4088</v>
+        <v>4089</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2135065962402081</v>
+        <v>-0.2137292923578542</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03184120146691072</v>
+        <v>-0.03211675417608717</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2183485587754603</v>
+        <v>-0.2185808254263861</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1236538614825022</v>
+        <v>-0.1239086721569009</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.06304017939926609</v>
+        <v>-0.06331273484444466</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1013072779801689</v>
+        <v>0.1009960336686078</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1276143211627172</v>
+        <v>0.1272960650083661</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.04021181022267939</v>
+        <v>0.03991229797681939</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.0659949036911911</v>
+        <v>0.06568863075283105</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03748083884151754</v>
+        <v>-0.03776644369123261</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.03298552758516138</v>
+        <v>-0.03327344813900623</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.0826499456019576</v>
+        <v>-0.08292568650617227</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.09787609746317827</v>
+        <v>-0.09815046618547996</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.07893597906844008</v>
+        <v>-0.07868711548518803</v>
       </c>
     </row>
     <row r="7">
@@ -2238,49 +2238,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4078</v>
+        <v>4079</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1834896524025922</v>
+        <v>-0.1837508301433459</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.02188234882216022</v>
+        <v>-0.02219256603279263</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1834218478901732</v>
+        <v>-0.1836950242456368</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.137729268415768</v>
+        <v>-0.1380130015953824</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.07565332218655385</v>
+        <v>-0.07595553038501635</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1128391283533929</v>
+        <v>0.1124923877716029</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1394208201173086</v>
+        <v>0.1390669174618608</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.05295112391218026</v>
+        <v>0.05261549305455304</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1034416798127893</v>
+        <v>0.1030931696327357</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.001804237427329269</v>
+        <v>0.001475479895439946</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.01768188443760721</v>
+        <v>-0.0180072267910063</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.06754855052069075</v>
+        <v>-0.06786163072688112</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.0572622272689145</v>
+        <v>-0.05758044844732524</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.06339989167668847</v>
+        <v>-0.0631286576827037</v>
       </c>
     </row>
     <row r="8">
@@ -2290,49 +2290,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4072</v>
+        <v>4073</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.1800968269419272</v>
+        <v>-0.1803776066479088</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.04036942582849434</v>
+        <v>-0.04069453485889341</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.250554164140155</v>
+        <v>-0.250830413348325</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.180504528231431</v>
+        <v>-0.1807972748799713</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09305239780520225</v>
+        <v>-0.09337005896785655</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07076576449976812</v>
+        <v>0.07040964767259794</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1465325062981009</v>
+        <v>0.1461571250573925</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.03610287725866357</v>
+        <v>0.03575149460052529</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1358090560206406</v>
+        <v>0.1354326765735436</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08434906550761667</v>
+        <v>0.08397984976156181</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.04061610880655309</v>
+        <v>0.040256175233921</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.05845212844671011</v>
+        <v>-0.05878770893158247</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.02297740793806469</v>
+        <v>-0.02332447801791915</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.05404161192361556</v>
+        <v>-0.05375691194916499</v>
       </c>
     </row>
     <row r="9">
@@ -2342,49 +2342,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4056</v>
+        <v>4057</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2201525005982745</v>
+        <v>-0.2204737700920916</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.1227110482184841</v>
+        <v>-0.123067962870735</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.3321894669161409</v>
+        <v>-0.332497893800614</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2623968136070047</v>
+        <v>-0.2627216374474273</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.147901120759478</v>
+        <v>-0.1482581342894775</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.01537746744867263</v>
+        <v>0.01498223723579173</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1163749793794437</v>
+        <v>0.1159540989650552</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.01727525458640855</v>
+        <v>-0.0176667898754701</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1569243787205679</v>
+        <v>0.156489329352965</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1332475799403028</v>
+        <v>0.1328120534311665</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.09016138953543162</v>
+        <v>0.08973480056446448</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.009420814458309223</v>
+        <v>-0.009822824413809883</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.003214542140369758</v>
+        <v>0.002806200051409746</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.02895083951533195</v>
+        <v>-0.02863006889795372</v>
       </c>
     </row>
     <row r="10">
@@ -2394,49 +2394,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4044</v>
+        <v>4045</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3366722368971864</v>
+        <v>-0.3370027727719105</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1848935899789623</v>
+        <v>-0.1852744183972916</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3938387162196477</v>
+        <v>-0.3941713387279719</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.299573239773089</v>
+        <v>-0.2999282661212064</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1584805011646822</v>
+        <v>-0.1588747703519218</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.004398151314326526</v>
+        <v>0.003965842837949651</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.08125786898053633</v>
+        <v>0.08080571302169659</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.05141278946249628</v>
+        <v>-0.05183610283108209</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1234754723204006</v>
+        <v>0.1230082855321868</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.07753679896715227</v>
+        <v>0.07707401212979903</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.01020654995738823</v>
+        <v>0.009758554921056373</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.08979274231505485</v>
+        <v>-0.0902159728428984</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.07589303276640891</v>
+        <v>-0.07632323968146437</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1089144352287548</v>
+        <v>-0.1085420036789913</v>
       </c>
     </row>
     <row r="11">
@@ -2446,49 +2446,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4031</v>
+        <v>4032</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3421030086372738</v>
+        <v>-0.3424735089027067</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1599216536788077</v>
+        <v>-0.1603513817584101</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3930028564952153</v>
+        <v>-0.3933785788454287</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.348345646237803</v>
+        <v>-0.3487314919296338</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.2050784252057838</v>
+        <v>-0.205504609273568</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.04264441759732307</v>
+        <v>-0.04310844268090364</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.03472388651893965</v>
+        <v>0.03423974111940709</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.04733935759615093</v>
+        <v>-0.04780747770729477</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.128309711757467</v>
+        <v>0.1277973202939719</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.06018002449869186</v>
+        <v>0.05967686944678974</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.03150095747970738</v>
+        <v>-0.03198341626976742</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1567391982650364</v>
+        <v>-0.1571905485980949</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1414562893834272</v>
+        <v>-0.1419153229872734</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1505980636662301</v>
+        <v>-0.1501804658211583</v>
       </c>
     </row>
     <row r="12">
@@ -2498,49 +2498,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4013</v>
+        <v>4014</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4318387176267677</v>
+        <v>-0.4322445629406104</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2168131754102589</v>
+        <v>-0.2172884127188937</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3994830254567105</v>
+        <v>-0.3999169866140946</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3800674773348334</v>
+        <v>-0.3805052236117845</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.2834838291474782</v>
+        <v>-0.283951092108623</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1465431187650381</v>
+        <v>-0.147041759931092</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.06847483015032196</v>
+        <v>-0.06899396895395427</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1239570929100111</v>
+        <v>-0.1244672693878286</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.07762106142725855</v>
+        <v>0.07705987382114898</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.03787704265479874</v>
+        <v>0.03731713147875126</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.0782030929141655</v>
+        <v>-0.07873638899811652</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1543553778593534</v>
+        <v>-0.1548696388805055</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1371187920526609</v>
+        <v>-0.1376417382185338</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1474205958447357</v>
+        <v>-0.1469551472931627</v>
       </c>
     </row>
     <row r="13">
@@ -2550,49 +2550,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3987</v>
+        <v>3988</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4684383202099767</v>
+        <v>-0.4689190297845443</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2415460667076132</v>
+        <v>-0.2421021235981868</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.4478546267643182</v>
+        <v>-0.448363880946367</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.4291721656571923</v>
+        <v>-0.429684883023981</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2533940675808353</v>
+        <v>-0.2539571823088949</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1174903890254626</v>
+        <v>-0.1180844087459931</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.03835502357478759</v>
+        <v>-0.03897011732892963</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.04106134109452597</v>
+        <v>-0.04168139904001578</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.08709745572905803</v>
+        <v>0.08644429855497293</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1278042980733431</v>
+        <v>0.1271309053679914</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.06244983422439532</v>
+        <v>0.06179015170551594</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.01438765216786919</v>
+        <v>-0.01502800291807915</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.005736280389378123</v>
+        <v>0.005085756164376676</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.04393767537700199</v>
+        <v>0.04442617155126527</v>
       </c>
     </row>
     <row r="14">
@@ -2602,49 +2602,49 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3964</v>
+        <v>3965</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4692995221209628</v>
+        <v>-0.4698551959440991</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1814706856893267</v>
+        <v>-0.1821197248051263</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4118303253054165</v>
+        <v>-0.4124268282727428</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4692752172790762</v>
+        <v>-0.4698559119346655</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3397124524141972</v>
+        <v>-0.3403329858021706</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.154413431045505</v>
+        <v>-0.1550771024212878</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.07433823536047868</v>
+        <v>-0.07502349220462889</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1247405252587441</v>
+        <v>-0.1254194463022955</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.02968860931363082</v>
+        <v>0.02896966252630762</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.07554457660326364</v>
+        <v>0.07480276710607114</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.01422281538551573</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.01608167027388419</v>
+        <v>-0.01680330075430447</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.006596363792176874</v>
+        <v>0.005863234623483038</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.06879773393765021</v>
+        <v>0.06934329366161762</v>
       </c>
     </row>
     <row r="15">
@@ -2654,49 +2654,49 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3931</v>
+        <v>3932</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4143308151389746</v>
+        <v>-0.4150098201414565</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1105914411630664</v>
+        <v>-0.1113719004744524</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.3649237650879158</v>
+        <v>-0.365646016595683</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4493027165010588</v>
+        <v>-0.4500019923650527</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.339520803453766</v>
+        <v>-0.3402563649552022</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05361262356527874</v>
+        <v>-0.05441668010364253</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.002475648538002417</v>
+        <v>0.001655683963058152</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.01901361355304232</v>
+        <v>-0.01983552713413417</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.08643556283758613</v>
+        <v>0.08558554402003438</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.08899397611958904</v>
+        <v>0.08813013960883609</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.02561397232766183</v>
+        <v>0.02476274856178406</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.09973880683262593</v>
+        <v>0.09886883883041264</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.1261636867182361</v>
+        <v>0.1252802625800271</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.2122600984746583</v>
+        <v>0.212861283601562</v>
       </c>
     </row>
     <row r="16">
@@ -2706,49 +2706,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3907</v>
+        <v>3908</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3250709732712025</v>
+        <v>-0.3258535464741641</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.08612956522322435</v>
+        <v>-0.08700008278185578</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3906412319096688</v>
+        <v>-0.3914410000602899</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5018715714982704</v>
+        <v>-0.5026412182615445</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3625941767809522</v>
+        <v>-0.3634086863057888</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1278481638301798</v>
+        <v>-0.1287181272448805</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.04536605110227754</v>
+        <v>-0.046258921821142</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.01302223944404801</v>
+        <v>-0.01393154738465796</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.1956991171295641</v>
+        <v>0.194735008421695</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2035179931867503</v>
+        <v>0.2025373419630583</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1154595964816991</v>
+        <v>0.1144975954098726</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.2154334066520391</v>
+        <v>0.2144459376879055</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3213966699511133</v>
+        <v>0.3203746476356244</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3809428474845333</v>
+        <v>0.3815686121791941</v>
       </c>
     </row>
     <row r="17">
@@ -2761,46 +2761,46 @@
         <v>3869</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3553651620440803</v>
+        <v>-0.3686027899367232</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.04677951884803377</v>
+        <v>-0.03386970927198263</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.2988497119357731</v>
+        <v>-0.285842580518171</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.4124220418372033</v>
+        <v>-0.3994428994387391</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2406944158920155</v>
+        <v>-0.2275836115170762</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.08391088562893145</v>
+        <v>-0.07086798933456606</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.0002219337084028439</v>
+        <v>0.01328818800887888</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.01413680379940985</v>
+        <v>-0.0009557945041720473</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2746692953297867</v>
+        <v>0.2878680342845499</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.3167460708187946</v>
+        <v>0.3301511984716257</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2298621667085001</v>
+        <v>0.2433194604187179</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3821756429541594</v>
+        <v>0.3956279316742695</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4416694027538952</v>
+        <v>0.4552254491054981</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.4993788309599978</v>
+        <v>0.5147956672184222</v>
       </c>
     </row>
     <row r="18">
@@ -2810,49 +2810,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3820</v>
+        <v>3821</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2367203447338468</v>
+        <v>-0.2378278719532361</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.06012675572120685</v>
+        <v>-0.06131683792116149</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2320654479149056</v>
+        <v>-0.2332200636768107</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.296520457554962</v>
+        <v>-0.2976559345899688</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.246257131741892</v>
+        <v>-0.2474183356151229</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.09127554105066338</v>
+        <v>-0.09247117472324362</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.02114760899962675</v>
+        <v>0.01992010987513737</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.06486763105210258</v>
+        <v>0.06361765222828808</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2013128145512795</v>
+        <v>0.2000251874314714</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3071041662914737</v>
+        <v>0.3057692277644151</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2478859591954645</v>
+        <v>0.2465612737594256</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.375551766529199</v>
+        <v>0.3741938091323149</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4673671819923797</v>
+        <v>0.4659751276292567</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5226203574445023</v>
+        <v>0.5234607628939969</v>
       </c>
     </row>
     <row r="19">
@@ -2862,49 +2862,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3776</v>
+        <v>3777</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2632984416140403</v>
+        <v>-0.2645571914842151</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.09234033866525948</v>
+        <v>-0.09368565487292813</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1296667501484379</v>
+        <v>-0.1310128958928161</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1963575652721445</v>
+        <v>-0.1976834849127371</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1128043365023359</v>
+        <v>-0.1141666553143281</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.04055600617783739</v>
+        <v>0.03916002194625889</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2081752264658903</v>
+        <v>0.2067320950030833</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2050065066183535</v>
+        <v>0.2035516368738897</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2908903893879682</v>
+        <v>0.2894105418339663</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.354922456787591</v>
+        <v>0.3534033391538358</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3238734382198345</v>
+        <v>0.3223565849103878</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4261767320751417</v>
+        <v>0.4246329382679122</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5239708889011823</v>
+        <v>0.5223897609175197</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.5769730063042147</v>
+        <v>0.5779303111875436</v>
       </c>
     </row>
     <row r="20">
@@ -2914,49 +2914,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3731</v>
+        <v>3732</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3032673800390313</v>
+        <v>-0.3046810505610509</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.02269311625135373</v>
+        <v>0.02114573964967548</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.143921259760134</v>
+        <v>-0.1454361586337427</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2129848982352271</v>
+        <v>-0.2144784021780097</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.06847652972212614</v>
+        <v>-0.07002479302762055</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.08316160274949169</v>
+        <v>0.08158049680126567</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2003256298290808</v>
+        <v>0.1987099728881461</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2027423557817514</v>
+        <v>0.2011118973786594</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2636282475053306</v>
+        <v>0.2619789393543215</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3654407203178991</v>
+        <v>0.3637390252480088</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3632688340539048</v>
+        <v>0.3615610217051923</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5199776466712862</v>
+        <v>0.5182280080251829</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6508387904920383</v>
+        <v>0.6490412036959867</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7293587828901096</v>
       </c>
     </row>
     <row r="21">
@@ -2966,49 +2966,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3673</v>
+        <v>3674</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2959342507579947</v>
+        <v>-0.2975691360401882</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.06052402340650076</v>
+        <v>0.05873889647778441</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1296309112149032</v>
+        <v>-0.1313782573355837</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1746777379534379</v>
+        <v>-0.1764094939722369</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1280378585744373</v>
+        <v>-0.1298008013794174</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.02128672267929232</v>
+        <v>0.01949205962896627</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1416160199470227</v>
+        <v>0.139784975545588</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.178601405216007</v>
+        <v>0.1767440652433621</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2685914932875875</v>
+        <v>0.2667067543189887</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.439813089679312</v>
+        <v>0.4378529476036306</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4680612512326405</v>
+        <v>0.4660857291834475</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.5450965075025138</v>
+        <v>0.543100179343881</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6574464462708036</v>
+        <v>0.6554047456303067</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7594198123603206</v>
+        <v>0.7606466893922175</v>
       </c>
     </row>
     <row r="22">
@@ -3018,49 +3018,49 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3605</v>
+        <v>3606</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.4481094092094224</v>
+        <v>-0.449968254905734</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.05469399012751097</v>
+        <v>-0.05672346135384032</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3516505512752488</v>
+        <v>-0.3536139009437633</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4000562761813029</v>
+        <v>-0.4020023470657463</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3148002440949256</v>
+        <v>-0.3167913065189225</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.08528157001664738</v>
+        <v>-0.08732592475009682</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.06447360747653619</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1684093589112976</v>
+        <v>0.1662717266618259</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2335399251554477</v>
+        <v>0.2313808508418873</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4517043116741846</v>
+        <v>0.4494514467277213</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4843471495748588</v>
+        <v>0.4820763331588154</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5621910081805197</v>
+        <v>0.5598987818931676</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6845892564000593</v>
+        <v>0.6822459783806778</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7560439764727676</v>
+        <v>0.7574916018966604</v>
       </c>
     </row>
     <row r="23">
@@ -3070,153 +3070,153 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3533</v>
+        <v>3534</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.2937767296854403</v>
+        <v>-0.29597100657044</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1686128905211106</v>
+        <v>0.1662171093403444</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1262914749852726</v>
+        <v>-0.1286224505252989</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1500395873213805</v>
+        <v>-0.1523594257129446</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3061289029243639</v>
+        <v>-0.3084293093366952</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.06321417001278462</v>
+        <v>0.06082120494223631</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1916651479254057</v>
+        <v>0.1892309770212179</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2486091878694552</v>
+        <v>0.2461373347103333</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3163292375516065</v>
+        <v>0.3138343192516899</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5279908359628323</v>
+        <v>0.5253977612957854</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6786112785592096</v>
+        <v>0.6759653736336801</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.6725296589809346</v>
+        <v>0.6698856386519054</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.8060148750868876</v>
+        <v>0.8033134140481692</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8738710187486163</v>
+        <v>0.8755272847380269</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.07097</t>
+          <t>X &gt; -0.07096</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3451</v>
+        <v>3452</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2417062185933432</v>
+        <v>-0.2442637938821193</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1254241049430007</v>
+        <v>0.1226784768637188</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.08046989453685427</v>
+        <v>-0.0831772912004638</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3101071373280107</v>
+        <v>-0.3127431076880285</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4571816702123712</v>
+        <v>-0.4598035636276663</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.05837268931653483</v>
+        <v>0.0556153025259789</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1051221934074249</v>
+        <v>0.1023455848298482</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1744734960130288</v>
+        <v>0.1716519034006296</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.2452262132440879</v>
+        <v>0.2423796094160977</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4531238212697062</v>
+        <v>0.4501728225356558</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5832074317503526</v>
+        <v>0.580206951299111</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.576137246995529</v>
+        <v>0.5731389982559492</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6937795527324866</v>
+        <v>0.6907245208036201</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8152360496863835</v>
+        <v>0.8171963941541804</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.06452</t>
+          <t>X &gt; -0.06451</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3346</v>
+        <v>3347</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3648286149405493</v>
+        <v>-0.3678207924391117</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2634395686715578</v>
+        <v>-0.2665588071349489</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.195442153026697</v>
+        <v>-0.1986066828618576</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3767788778427033</v>
+        <v>-0.3798833960427928</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6606567699255024</v>
+        <v>-0.6637102658939256</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.1979651625758834</v>
+        <v>-0.2011406393432011</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.05770256561555698</v>
+        <v>-0.06092660288817342</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.0880727581376064</v>
+        <v>0.0847758083935588</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.07340250390359415</v>
+        <v>0.07010454647092246</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4039629685146693</v>
+        <v>0.4005141385607232</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4250912840717618</v>
+        <v>0.4216221617879015</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4764109687708995</v>
+        <v>0.4729267301373028</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6407755481778068</v>
+        <v>0.6372153910354186</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.6685318623123919</v>
+        <v>0.6709247290702507</v>
       </c>
     </row>
     <row r="26">
@@ -3226,49 +3226,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3234</v>
+        <v>3235</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4453939715804651</v>
+        <v>-0.4488963261008578</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.1000827896129266</v>
+        <v>-0.1038052341617757</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2934091451637357</v>
+        <v>-0.297101481242926</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6704906390991994</v>
+        <v>-0.6740597669220207</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.6989830423095</v>
+        <v>-0.7025828007212169</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.261439603767208</v>
+        <v>-0.2651556242723387</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.04085203137665872</v>
+        <v>0.03703482098461564</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.2078464697967561</v>
+        <v>0.2039431315540838</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.225688933219395</v>
+        <v>0.2217737176309527</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.5044856792353158</v>
+        <v>0.500423028360494</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.6261389457892221</v>
+        <v>0.6220222613518445</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5853998970907384</v>
+        <v>0.5812959859233473</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.7391265594181249</v>
+        <v>0.7349436069102993</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.7283047254325368</v>
+        <v>0.7311230473409296</v>
       </c>
     </row>
     <row r="27">
@@ -3278,49 +3278,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3113</v>
+        <v>3114</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5420627603891219</v>
+        <v>-0.5461542780559441</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.025011933174234</v>
+        <v>-0.02940218757770907</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5306104733175587</v>
+        <v>-0.5348735083532219</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8313630178901903</v>
+        <v>-0.8355216042014817</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.744051284695459</v>
+        <v>-0.748284059391132</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3010906038085182</v>
+        <v>-0.3054434526072711</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1440584505100659</v>
+        <v>-0.1484709793083567</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1436639801573918</v>
+        <v>0.1391186471831674</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.03625812472580492</v>
+        <v>0.03173971654639729</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4550645347929958</v>
+        <v>0.4503398633738058</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.525192055631571</v>
+        <v>0.5204255462132323</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.6099134455136763</v>
+        <v>0.6051199278845374</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.7538380036709782</v>
+        <v>0.7489612693633916</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.7650171296361137</v>
+        <v>0.7683384349954139</v>
       </c>
     </row>
     <row r="28">
@@ -3330,49 +3330,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2955</v>
+        <v>2956</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3356500531836772</v>
+        <v>-0.3407070652495534</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.2288835137060303</v>
+        <v>0.223474410454422</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4357996954200658</v>
+        <v>-0.4227925640024637</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.489735469376555</v>
+        <v>-0.4949282973112332</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3012313074531789</v>
+        <v>-0.3065438557822802</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.06370978652302739</v>
+        <v>0.07675268281739278</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2337614563442827</v>
+        <v>0.2282893704631448</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.6969830227630993</v>
+        <v>0.6913053193900893</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.5535032402711124</v>
+        <v>0.5478647529418481</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.074036056942084</v>
+        <v>1.068134534247363</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.023828941221105</v>
+        <v>1.017920830660508</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.246680895062063</v>
+        <v>1.240697517780212</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.319488090623878</v>
+        <v>1.313435154276689</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.318104096957804</v>
+        <v>1.321973291938136</v>
       </c>
     </row>
     <row r="29">
@@ -3382,49 +3382,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2785</v>
+        <v>2786</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5435277656482569</v>
+        <v>-0.5495855584313531</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.04674182487873679</v>
+        <v>0.04027712506012904</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.562872765755067</v>
+        <v>-0.5498656343374648</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4849157277147</v>
+        <v>-0.4912224520948527</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5578876051570845</v>
+        <v>-0.5447768007821452</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1691998749860701</v>
+        <v>0.1822427712804355</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3906193835947036</v>
+        <v>0.3839627736326108</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.8030798256893803</v>
+        <v>0.7962158479766472</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.6187701200541227</v>
+        <v>0.6119608712242908</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.079452498277114</v>
+        <v>1.072372643324194</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.074538880369168</v>
+        <v>1.067432193736451</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.380666903583446</v>
+        <v>1.373450366606875</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.232352237377356</v>
+        <v>1.225134467443674</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.287422447925493</v>
+        <v>1.292175161521904</v>
       </c>
     </row>
     <row r="30">
@@ -3434,49 +3434,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.3851211055097821</v>
+        <v>-0.4112835353699467</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.3454524631105969</v>
+        <v>0.3196625822841668</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7073109803280957</v>
+        <v>-0.7121929044043185</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5175175574923969</v>
+        <v>-0.5432530879549518</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.5139333525103638</v>
+        <v>-0.518485555350864</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2867993323984805</v>
+        <v>0.2823741443074468</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.6880832007640478</v>
+        <v>0.6624197881396583</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.094740725540298</v>
+        <v>1.069177062228022</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.9780266008409839</v>
+        <v>0.9524656498732682</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.312934975482541</v>
+        <v>1.28756538425209</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.401970085589817</v>
+        <v>1.376637619796533</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.730369685458221</v>
+        <v>1.705017162381665</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.643179666448177</v>
+        <v>1.617915837023382</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.582341992513292</v>
+        <v>1.555600471149084</v>
       </c>
     </row>
     <row r="31">
@@ -3489,46 +3489,46 @@
         <v>2381</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6927683034595589</v>
+        <v>-0.6802460137839361</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06340029975412875</v>
+        <v>0.05362651961790021</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.253127393017579</v>
+        <v>-1.240120261599976</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.039087079848699</v>
+        <v>-1.026107937450234</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.032891621271936</v>
+        <v>-1.019780816896997</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1070458293459708</v>
+        <v>-0.09400293305160545</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.3947307173113686</v>
+        <v>0.4077969716118446</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.124148354246167</v>
+        <v>1.113748855684342</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.128677471105725</v>
+        <v>1.1182583553841</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.560579216135629</v>
+        <v>1.549819048950752</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.631794934280457</v>
+        <v>1.620961037877251</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.984360374258287</v>
+        <v>1.973377757601561</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.092551113801839</v>
+        <v>2.081440147196474</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.712285045826135</v>
+        <v>1.701855410127983</v>
       </c>
     </row>
     <row r="32">
@@ -3541,46 +3541,46 @@
         <v>2113</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3933911281382478</v>
+        <v>-0.3808688384626251</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4018309172268957</v>
+        <v>0.4147407268029468</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.078455439204511</v>
+        <v>-1.065448307786909</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6650498762053303</v>
+        <v>-0.6520707338068661</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4955900152982551</v>
+        <v>-0.4824792109233158</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.08500435280909358</v>
+        <v>0.09804724910345897</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5193834245882627</v>
+        <v>0.5324496788887387</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.164199423316852</v>
+        <v>1.150798684936831</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.507699642625283</v>
+        <v>1.494113101396209</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.913118514038473</v>
+        <v>1.899132632014478</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.019470044324109</v>
+        <v>2.005376358667398</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.601770832861803</v>
+        <v>2.587400053037406</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.540648162272603</v>
+        <v>2.526198096083064</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>2.506413034539435</v>
+        <v>2.495983398841283</v>
       </c>
     </row>
     <row r="33">
@@ -3593,98 +3593,98 @@
         <v>1763</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9388877266542934</v>
+        <v>-0.9263654369786707</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.6716980724786765</v>
+        <v>0.6846078820547277</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.079869333948324</v>
+        <v>-1.066862202530722</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.119203538819626</v>
+        <v>-1.106224396421162</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.035804516469518</v>
+        <v>-1.022693712094579</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5687752412750626</v>
+        <v>-0.5557323449806972</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.1447469461109421</v>
+        <v>-0.131680691810466</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.7198290406028605</v>
+        <v>0.7014202517402808</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.030013281721729</v>
+        <v>1.011394409212429</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.250246837955686</v>
+        <v>2.230644667470571</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.475138780385826</v>
+        <v>2.455326798288304</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.166411700246286</v>
+        <v>3.146203688207748</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.347070549788619</v>
+        <v>3.32660655968926</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.483348887169832</v>
+        <v>3.47291925147168</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.006452</t>
+          <t>X &gt; -0.006451</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>1395</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.4220097487814058</v>
+        <v>-0.4094874591057831</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.466416638254337</v>
+        <v>1.479326447830388</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.5001193602291849</v>
+        <v>0.513126491646787</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4410560785918989</v>
+        <v>-0.4280769361934347</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.4794772936640683</v>
+        <v>-0.466366489289129</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4677496416626852</v>
+        <v>-0.4547067453683198</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2332309267793136</v>
+        <v>0.2462971810797896</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.051761813712105</v>
+        <v>1.064942823007343</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.8165048050954056</v>
+        <v>0.7896749521988582</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.366980498888552</v>
+        <v>2.338612481816092</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.633551891443318</v>
+        <v>2.604869017637412</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.569734442905897</v>
+        <v>3.54037087365775</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.264041662485496</v>
+        <v>3.23466911613496</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>3.575017946877246</v>
       </c>
     </row>
     <row r="35">
@@ -3759,7 +3759,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that Drawdown-7 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that Drawdown-7 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3855,46 +3855,46 @@
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.41132358455193</v>
+        <v>9.423845874227553</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.037845209682906</v>
+        <v>3.050755019258958</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.78583364594347</v>
+        <v>9.798840777361072</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.344658207122386</v>
+        <v>6.35763734952085</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.425284611097844</v>
+        <v>3.438395415472783</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.420130594043641</v>
+        <v>-3.407087697749276</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.50486431131592</v>
+        <v>-3.491798057015444</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.7898570518073456</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.728857165625044</v>
+        <v>0.7420559045798072</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.831112932978066</v>
+        <v>5.844518060630897</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.626359608660486</v>
+        <v>5.639816902370704</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.041695146958304</v>
+        <v>8.055147435678414</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.811916726489592</v>
+        <v>8.825472772841195</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.87116186828969</v>
+        <v>7.860732232591538</v>
       </c>
     </row>
     <row r="7">
@@ -3907,46 +3907,46 @@
         <v>94</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.081029764896407</v>
+        <v>7.093552054572029</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.277966790230018</v>
+        <v>2.290876599806069</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.202247019803643</v>
+        <v>7.215254151221245</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.268670365177108</v>
+        <v>6.281649507575572</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.602589575636848</v>
+        <v>3.615700380011788</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.546776997285789</v>
+        <v>-3.533734100991424</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.631510714558068</v>
+        <v>-3.618444460257592</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1566250355966048</v>
+        <v>0.1698060448918426</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.9682046378197455</v>
+        <v>-0.9550058988649823</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.500819113322542</v>
+        <v>3.514224240975373</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.359895576239012</v>
+        <v>4.37335286994923</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.521938308052519</v>
+        <v>6.535390596772629</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.101683697107617</v>
+        <v>6.11523974345922</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.351405029383905</v>
+        <v>6.340975393685753</v>
       </c>
     </row>
     <row r="8">
@@ -3959,46 +3959,46 @@
         <v>100</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.506561679790025</v>
+        <v>6.519083969465647</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.894988066825761</v>
+        <v>2.907897876401812</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.500119360229178</v>
+        <v>9.51312649164678</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.630372492836678</v>
+        <v>7.643351635235142</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.091951277764508</v>
+        <v>4.105062082139447</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.610606784519831</v>
+        <v>-1.597563888225466</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.69534050179211</v>
+        <v>-3.682274247491634</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.8374760994263966</v>
+        <v>0.8506571087216344</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.223523786755912</v>
+        <v>-2.210325047801149</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.07364897178383245</v>
+        <v>-0.06024384413100137</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.721597703898574</v>
+        <v>1.735054997608792</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.755980861244012</v>
+        <v>5.769433149964122</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.335726250299111</v>
+        <v>4.349282296650713</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.585447582575398</v>
+        <v>5.575017946877246</v>
       </c>
     </row>
     <row r="9">
@@ -4011,46 +4011,46 @@
         <v>116</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>6.989320300479683</v>
+        <v>7.001842590155306</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.377746687515426</v>
+        <v>5.390656497091477</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>11.01736073953953</v>
+        <v>11.03036787095713</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.423475941112542</v>
+        <v>9.436455083511007</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.436778863971405</v>
+        <v>5.449889668346344</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5618070085836138</v>
+        <v>0.5748499048779792</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.109133605240388</v>
+        <v>-2.096067350939911</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.596096789081564</v>
+        <v>2.609277798376802</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.63731689020419</v>
+        <v>-2.624118151249426</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.763304144197633</v>
+        <v>-1.749899016544802</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2439195374807355</v>
+        <v>-0.2304622437705177</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.238739481933671</v>
+        <v>3.252191770653781</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.818484870988769</v>
+        <v>2.832040917340372</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.930275168782295</v>
+        <v>3.919845533084143</v>
       </c>
     </row>
     <row r="10">
@@ -4063,46 +4063,46 @@
         <v>128</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>10.01908396946565</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.832488066825768</v>
+        <v>6.845397876401819</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>11.90636936022918</v>
+        <v>11.91937649164678</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.692872492836678</v>
+        <v>9.705851635235142</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.248201277764508</v>
+        <v>5.261312082139447</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8581432154801689</v>
+        <v>0.8711861117745343</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7890905017921099</v>
+        <v>-0.7760242474916339</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.431226099426389</v>
+        <v>3.444407108721627</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.317273786755912</v>
+        <v>-1.304075047801149</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1763510282161604</v>
+        <v>0.1897561558689915</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.315347703898581</v>
+        <v>2.328804997608799</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.474730861244012</v>
+        <v>5.488183149964122</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.054476250299111</v>
+        <v>5.068032296650713</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.085447582575398</v>
+        <v>6.075017946877246</v>
       </c>
     </row>
     <row r="11">
@@ -4115,46 +4115,46 @@
         <v>141</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.20868933936449</v>
+        <v>9.221211629040113</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.46945615193215</v>
+        <v>5.482365961508201</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.7483463105838</v>
+        <v>10.7613534420014</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.16937958503527</v>
+        <v>10.18235872743373</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.084859079182948</v>
+        <v>6.097969883557887</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.126981867962442</v>
+        <v>2.140024764256808</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6238084343781054</v>
+        <v>0.6368746886785814</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.993504468220713</v>
+        <v>3.006685477515951</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.322814566897755</v>
+        <v>-1.309615827942991</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.6639396806984337</v>
+        <v>0.6773448083512648</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.296065789004963</v>
+        <v>3.309523082715181</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.876548237130542</v>
+        <v>6.890000525850652</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.456293626185641</v>
+        <v>6.469849672537244</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>6.706014958461928</v>
+        <v>6.695585322763776</v>
       </c>
     </row>
     <row r="12">
@@ -4167,46 +4167,46 @@
         <v>159</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>10.39964344079631</v>
+        <v>10.41216573047193</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.272346557391806</v>
+        <v>6.285256366967857</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.651062756455588</v>
+        <v>9.66406988787319</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.781315889063087</v>
+        <v>9.794295031461552</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.356102221160732</v>
+        <v>7.369213025535672</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.508890070826077</v>
+        <v>4.521932967120442</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.166294718333674</v>
+        <v>3.17936097263415</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.585903772382359</v>
+        <v>4.599084781677597</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1223881629296244</v>
+        <v>0.1355869018843876</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.159055430731883</v>
+        <v>1.172460558384714</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.09895619446462</v>
+        <v>4.112413488174838</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.020131804640236</v>
+        <v>6.033584093360346</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.599877193695335</v>
+        <v>5.613433240046938</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.849598525971622</v>
+        <v>5.83916889027347</v>
       </c>
     </row>
     <row r="13">
@@ -4219,46 +4219,46 @@
         <v>185</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.668723841952186</v>
+        <v>9.681246131627809</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.894988066825768</v>
+        <v>5.907897876401819</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.283903144012967</v>
+        <v>9.296910275430569</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.414156276620467</v>
+        <v>9.427135419018931</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.632491818305056</v>
+        <v>5.645602622679995</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.227231053318008</v>
+        <v>3.240273949612373</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.061416254964648</v>
+        <v>2.074482509265124</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.134773396723688</v>
+        <v>2.147954406018926</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.08838865162077525</v>
+        <v>-0.07518991266601205</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9385138366487027</v>
+        <v>-0.9251087089958716</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4783544606553392</v>
+        <v>0.4918117543655569</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.134359239622391</v>
+        <v>2.147811528342501</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.714104628677489</v>
+        <v>1.727660675029092</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8827448798726962</v>
+        <v>0.8723152441745441</v>
       </c>
     </row>
     <row r="14">
@@ -4271,46 +4271,46 @@
         <v>208</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.564253987482338</v>
+        <v>8.576776277157961</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.068064989902695</v>
+        <v>4.080974799478746</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.519350129459951</v>
+        <v>7.532357260877554</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9.091910954375138</v>
+        <v>9.104890096773602</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.630412816226048</v>
+        <v>6.643523620600988</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.562470138557096</v>
+        <v>3.575513034851461</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.51619795974635</v>
+        <v>2.529264214046826</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.491322253272543</v>
+        <v>3.504503262567781</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.026476213244088</v>
+        <v>1.039674952198851</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1763510282161604</v>
+        <v>0.1897561558689915</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.894674626975508</v>
+        <v>1.908131920685726</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.929057784320939</v>
+        <v>1.942510073041049</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.508803173376037</v>
+        <v>1.52235921972764</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3162168133446244</v>
+        <v>0.3057871776464722</v>
       </c>
     </row>
     <row r="15">
@@ -4323,46 +4323,46 @@
         <v>241</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>6.42772350551617</v>
+        <v>6.440245795191792</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.32652333653531</v>
+        <v>2.339433146111361</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.666094463963617</v>
+        <v>5.679101595381219</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7.456098633915516</v>
+        <v>7.469077776313981</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.672864140835046</v>
+        <v>5.685974945209985</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.405990725853613</v>
+        <v>1.419033622147978</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9063192492452359</v>
+        <v>0.9193855035457119</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.269011369135931</v>
+        <v>1.282192378431169</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.03680179505466441</v>
+        <v>-0.02360305609990121</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.05705146141039563</v>
+        <v>-0.04364633375756455</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9830084922803195</v>
+        <v>0.9964657859905373</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2274216283825439</v>
+        <v>-0.2139693396624338</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6476762393274456</v>
+        <v>-0.6341201929758427</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.057705944395558</v>
+        <v>-2.06813558009371</v>
       </c>
     </row>
     <row r="16">
@@ -4375,46 +4375,46 @@
         <v>265</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.487693755261724</v>
+        <v>4.500216044937346</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.744044670599351</v>
+        <v>1.756954480175402</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.51312649164678</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7.517164945666863</v>
+        <v>7.530144088065327</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.469309768330547</v>
+        <v>5.482420572705486</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.370525290951868</v>
+        <v>2.383568187246233</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.531074592547512</v>
+        <v>1.544140846847988</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.063891193766011</v>
+        <v>1.077072203061249</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.638618126378553</v>
+        <v>-1.62541938742379</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.734026330274403</v>
+        <v>-1.720621202621572</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4293456923278356</v>
+        <v>-0.4158883986176178</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.904396497246552</v>
+        <v>-1.890944208526442</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.456726579889569</v>
+        <v>-3.443170533537966</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.339080719311397</v>
+        <v>-4.349510355009549</v>
       </c>
     </row>
     <row r="17">
@@ -4424,49 +4424,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.272238247446786</v>
+        <v>4.42697870630775</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.010499617980884</v>
+        <v>0.8421084027176065</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.58592794108727</v>
+        <v>3.407863333752047</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.366346090196416</v>
+        <v>5.182825319445676</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>3.177759858622601</v>
+        <v>2.999798924244715</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.495003776536279</v>
+        <v>1.323488743353487</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7502040526633422</v>
+        <v>0.5808836472452157</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.9430866604824999</v>
+        <v>0.7717097403005795</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.418243258703114</v>
+        <v>-2.578746100432731</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-2.938335440430706</v>
+        <v>-3.099717528341543</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.822956751546961</v>
+        <v>-1.988629212917516</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.768771614003512</v>
+        <v>-3.927935271088508</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.519059228248743</v>
+        <v>-4.677033492822972</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.25943690587345</v>
+        <v>-5.438139947859604</v>
       </c>
     </row>
     <row r="18">
@@ -4479,46 +4479,46 @@
         <v>352</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.336107134335485</v>
+        <v>2.348629424011108</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.008624430462135</v>
+        <v>1.021534240038186</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.318301178410998</v>
+        <v>2.3313083098286</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.300827038291217</v>
+        <v>3.313806180689681</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.762405823219048</v>
+        <v>2.775516627593987</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.355302306389262</v>
+        <v>1.368345202683628</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.4182958618442569</v>
+        <v>0.431362116144733</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.04888753693724368</v>
+        <v>-0.03570652764200588</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.246251059483185</v>
+        <v>-1.233052320528422</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.380467153602019</v>
+        <v>-2.367062025949188</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-1.719490456936661</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.119019138755988</v>
+        <v>-3.105566850035878</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.10745556788271</v>
+        <v>-4.093899521531107</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.710006962879142</v>
+        <v>-4.720436598577294</v>
       </c>
     </row>
     <row r="19">
@@ -4531,46 +4531,46 @@
         <v>396</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.304541477769824</v>
+        <v>2.317063767445447</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.198018369856065</v>
+        <v>1.210928179432116</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.943503805967993</v>
+        <v>1.956482948366457</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.152557338370563</v>
+        <v>1.165668142745503</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.06515223906529144</v>
+        <v>-0.05210934277092605</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.412512218963819</v>
+        <v>-1.399445964663343</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.374645112694829</v>
+        <v>-1.361464103399591</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.940695503927621</v>
+        <v>-1.927496764972858</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.538295436430303</v>
+        <v>-2.524890308777472</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.237998255697377</v>
+        <v>-2.224540961987159</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.213716108452957</v>
+        <v>-3.200263819732847</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.139021224448356</v>
+        <v>-4.125465178096754</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.646875649747841</v>
+        <v>-4.657305285445993</v>
       </c>
     </row>
     <row r="20">
@@ -4583,46 +4583,46 @@
         <v>441</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.381845126502043</v>
+        <v>2.394367416177666</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.08999940469424672</v>
+        <v>0.1029092142702979</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.055674915784735</v>
+        <v>1.068682047202337</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.866200157235774</v>
+        <v>1.879179299634238</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.6606176376950046</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4155954466513521</v>
+        <v>-0.4025525503569867</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.18060127276717</v>
+        <v>-1.167535018466694</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.194269932319642</v>
+        <v>-1.181088923024404</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.482027188116454</v>
+        <v>-1.468828449161691</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.332152373144382</v>
+        <v>-2.318747245491551</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.31014832784745</v>
+        <v>-2.296691034137233</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.636309388189098</v>
+        <v>-3.622857099468987</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.736836107977538</v>
+        <v>-4.723280061625935</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.394144254159293</v>
+        <v>-5.404573889857446</v>
       </c>
     </row>
     <row r="21">
@@ -4635,46 +4635,46 @@
         <v>499</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.015579715862167</v>
+        <v>2.028102005537789</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1971963019117098</v>
+        <v>-0.1842864923356586</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8107406027141479</v>
+        <v>0.8237477341317501</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.341795338528058</v>
+        <v>1.354774480926523</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.003774925059098</v>
+        <v>1.016885729434037</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.09881205315551966</v>
+        <v>0.1118549494498851</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.5871240689263786</v>
+        <v>-0.5740578146259026</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.8539066661046704</v>
+        <v>-0.8407256568094326</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.31570815549339</v>
+        <v>-1.302509416538626</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.566634943727728</v>
+        <v>-2.553229816074897</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.771388268045307</v>
+        <v>-2.757930974335089</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.338207515509495</v>
+        <v>-3.324755226789385</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.159263729660815</v>
+        <v>-4.145707683309212</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.911546405400557</v>
+        <v>-4.921976041098709</v>
       </c>
     </row>
     <row r="22">
@@ -4687,46 +4687,46 @@
         <v>567</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.709383549278563</v>
+        <v>2.721905838954186</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.5687094072137739</v>
+        <v>0.5816192167898251</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.113875973985792</v>
+        <v>2.126883105403394</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.596862792660311</v>
+        <v>2.609841935058775</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.058441577588141</v>
+        <v>2.07155238196308</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.768581928002213</v>
+        <v>0.7816248242965784</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.02161916140410369</v>
+        <v>-0.00855290710362766</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6651694032191102</v>
+        <v>-0.6519883939238724</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.9025361324349248</v>
+        <v>-0.8893373934801616</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.281761846563377</v>
+        <v>-2.268356718910546</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.486515170880956</v>
+        <v>-2.473057877170739</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.981232542636064</v>
+        <v>-2.967780253915954</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.754220839647985</v>
+        <v>-3.740664793296382</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.209966879505735</v>
+        <v>-4.220396515203888</v>
       </c>
     </row>
     <row r="23">
@@ -4739,150 +4739,150 @@
         <v>639</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.497172008428521</v>
+        <v>1.509694298104144</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.7403796953025505</v>
+        <v>-0.7274698857264994</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5861913477096152</v>
+        <v>0.5991984791272174</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8729390030088169</v>
+        <v>0.8859181454072811</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.742968492161999</v>
+        <v>1.756079296536939</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1505128878062152</v>
+        <v>-0.1374699915118498</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.7047301731536137</v>
+        <v>-0.6916639188531377</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.015419049243405</v>
+        <v>-1.002238039948168</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.232913458117416</v>
+        <v>-1.219714719162653</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.396027688528754</v>
+        <v>-2.382622560875923</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.226759103613155</v>
+        <v>-3.213301809902937</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.192375946267724</v>
+        <v>-3.178923657547614</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.925619602596043</v>
+        <v>-3.912063556244441</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.301876361086578</v>
+        <v>-4.31230599678473</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.07097</t>
+          <t>X &lt; -0.07096</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.04331618741832</v>
+        <v>1.055838477093943</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.429561170344833</v>
+        <v>-0.4166513607687818</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2851401646674532</v>
+        <v>0.2981472960850553</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.524963338883829</v>
+        <v>1.537942481282293</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.234808420621647</v>
+        <v>2.247919224996586</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.1029784904837712</v>
+        <v>-0.08993559418940578</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.18771220775605</v>
+        <v>-0.174645953455574</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5161993513364393</v>
+        <v>-0.5030183420412015</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.7158954927198522</v>
+        <v>-0.702696753765089</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.704716932948891</v>
+        <v>-1.69131180529606</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.325559022869797</v>
+        <v>-2.312101729159579</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.291175865524366</v>
+        <v>-2.277723576804256</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.850126731670379</v>
+        <v>-2.836570685318776</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.432582930600745</v>
+        <v>-3.443012566298897</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.06452</t>
+          <t>X &lt; -0.06451</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>826</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.380653689475253</v>
+        <v>1.393175979150875</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.221864580142956</v>
+        <v>1.234774389719007</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.7059304982437027</v>
+        <v>0.7189376296613048</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.562575882667183</v>
+        <v>1.575555025065647</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.719069921832308</v>
+        <v>2.732180726207247</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.958400479402691</v>
+        <v>0.9714433756970564</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.510470636222415</v>
+        <v>0.523536890522891</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.07777813786174903</v>
+        <v>-0.06459712856651123</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1033527265612761</v>
+        <v>0.1165514655160393</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.231033959677305</v>
+        <v>-1.217628832024474</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.314721908692221</v>
+        <v>-1.301264614982003</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.522469501952109</v>
+        <v>-1.509017213231999</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.184854863502338</v>
+        <v>-2.171298817150735</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.298329657134047</v>
+        <v>-2.3087592928322</v>
       </c>
     </row>
     <row r="26">
@@ -4895,46 +4895,46 @@
         <v>938</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.451124579576813</v>
+        <v>1.463646869252436</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.4792098152266178</v>
+        <v>0.4921196248026689</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9372195734487931</v>
+        <v>0.9502267048663953</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.346790403284437</v>
+        <v>2.359769545682902</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.448028036826344</v>
+        <v>2.461138841201283</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.039713044904481</v>
+        <v>1.052755941198846</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1021008628134368</v>
+        <v>0.1151671171139128</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4716923440704193</v>
+        <v>-0.4585113347751815</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4260824221503654</v>
+        <v>-0.4128836831956022</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.382817415280648</v>
+        <v>-1.369412287627817</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.80079035580291</v>
+        <v>-1.787333062092692</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.659797390355138</v>
+        <v>-1.646345101635028</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.186661809402381</v>
+        <v>-2.173105763050778</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.15016009333079</v>
+        <v>-2.160589729028942</v>
       </c>
     </row>
     <row r="27">
@@ -4947,46 +4947,46 @@
         <v>1059</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.519781698675772</v>
+        <v>1.532303988351394</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.1914942046916721</v>
+        <v>0.2044040142677233</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.496342211976113</v>
+        <v>1.509349343393716</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.476453701524115</v>
+        <v>2.489432843922579</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.221318605432124</v>
+        <v>2.234429409807063</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.007901241920209</v>
+        <v>1.020944138214574</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6398814056677509</v>
+        <v>0.6529476599682269</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.2050168184206314</v>
+        <v>-0.1918358091253936</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2061268270306869</v>
+        <v>0.2193255659854501</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.021713183304136</v>
+        <v>-1.008308055651305</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.226466507621716</v>
+        <v>-1.213009213911498</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.475369469256464</v>
+        <v>-1.461917180536354</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.895624080201365</v>
+        <v>-1.882068033849762</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.929188866905243</v>
+        <v>-1.939618502603395</v>
       </c>
     </row>
     <row r="28">
@@ -4999,46 +4999,46 @@
         <v>1217</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7469226313897011</v>
+        <v>0.7594449210653238</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4544787092201759</v>
+        <v>-0.4415688996441247</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.000940378291574</v>
+        <v>0.9684177139601573</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.213295317138815</v>
+        <v>1.226274459537279</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.7569759083063801</v>
+        <v>0.7700867126813193</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.05021237203009576</v>
+        <v>-0.08196454503991646</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3814538953829114</v>
+        <v>-0.3683876410824354</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.505991443712475</v>
+        <v>-1.492810434417237</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.073975717733724</v>
+        <v>-1.060776978778961</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.334947246229198</v>
+        <v>-2.321542118576367</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.211023495772736</v>
+        <v>-2.197566202062518</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.751825219281869</v>
+        <v>-2.738372930561759</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.925572024146248</v>
+        <v>-2.912015977794645</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.922358497950484</v>
+        <v>-2.932788133648636</v>
       </c>
     </row>
     <row r="29">
@@ -5051,46 +5051,46 @@
         <v>1387</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.031741535905141</v>
+        <v>1.044263825580764</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.004292508713803045</v>
+        <v>0.008617300862248101</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.079672995938324</v>
+        <v>1.052694836970524</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.9939434071635347</v>
+        <v>1.006922549561999</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.143824476611769</v>
+        <v>1.116581160613173</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2486745566899842</v>
+        <v>-0.2747973176202834</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6218004873725036</v>
+        <v>-0.6087342330720276</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.449474152916792</v>
+        <v>-1.436293143621555</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-1.005787665631182</v>
+        <v>-0.9925889266764187</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.928010904011664</v>
+        <v>-1.914605776358833</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.916470068271572</v>
+        <v>-1.903012774561354</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.53096939109917</v>
+        <v>-2.51751710237906</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.230243468518481</v>
+        <v>-2.216687422166878</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.341012403004996</v>
+        <v>-2.351442038703148</v>
       </c>
     </row>
     <row r="30">
@@ -5100,49 +5100,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.5690616797900248</v>
+        <v>0.6109015834569007</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.4800119331742323</v>
+        <v>-0.438135852517604</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.097367640404279</v>
+        <v>1.103382581590573</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.8523862514357958</v>
+        <v>0.8933516352351418</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.8491477733840327</v>
+        <v>0.8550620821394475</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3839317688654873</v>
+        <v>-0.3761755204956359</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9696047472523475</v>
+        <v>-0.9275808807832533</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.624640368951823</v>
+        <v>-1.582384192905401</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.372553216937497</v>
+        <v>-1.330475235535815</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.909591363768811</v>
+        <v>-1.867502917973304</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.051727280447075</v>
+        <v>-2.009625853455034</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.580900791855548</v>
+        <v>-2.538451706105967</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.437598734046546</v>
+        <v>-2.39539855441312</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.341870713163949</v>
+        <v>-2.294819349743527</v>
       </c>
     </row>
     <row r="31">
@@ -5152,49 +5152,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.8732839947594186</v>
+        <v>0.856125126306587</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.01486168275687305</v>
+        <v>-0.001951873180821906</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.624840963792657</v>
+        <v>1.606615640227744</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.396389205928607</v>
+        <v>1.37831822766276</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.390724967842552</v>
+        <v>1.37247155289154</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.213710002987149</v>
+        <v>0.1961930794445479</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.3984655017921099</v>
+        <v>-0.4156819440895134</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.367881043430749</v>
+        <v>-1.354700034135512</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.317273786755912</v>
+        <v>-1.304075047801149</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.888381114640978</v>
+        <v>-1.874975986988147</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.981527296101419</v>
+        <v>-1.968070002391201</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.449376281613127</v>
+        <v>-2.435923992893017</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.590613035415181</v>
+        <v>-2.577056989063578</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.087360904303438</v>
+        <v>-2.072303481694185</v>
       </c>
     </row>
     <row r="32">
@@ -5204,49 +5204,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.3623216023456948</v>
+        <v>0.3492726487109294</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3519852987916678</v>
+        <v>-0.3650934111102799</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.071824786585765</v>
+        <v>1.057920680508772</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.6958111743684299</v>
+        <v>0.6821113251576207</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5235710643794462</v>
+        <v>0.5098124456876718</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.02545394609187923</v>
+        <v>-0.03888299588792421</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4234958415979335</v>
+        <v>-0.4367623600583528</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.084853997660993</v>
+        <v>-1.071672988365755</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.388572330445236</v>
+        <v>-1.375373591490472</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.801804311589663</v>
+        <v>-1.788399183936832</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.90947025726647</v>
+        <v>-1.896012963556252</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.506155061086083</v>
+        <v>-2.492702772365973</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.440972778827103</v>
+        <v>-2.4274167324755</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.407753000231793</v>
+        <v>-2.395855839530519</v>
       </c>
     </row>
     <row r="33">
@@ -5256,101 +5256,101 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.6522570440284312</v>
+        <v>0.642791044351867</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4404156598823121</v>
+        <v>-0.4497180176379203</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.761096990717995</v>
+        <v>0.7512217297420207</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.8313671053522214</v>
+        <v>0.8214792242989404</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.7718849427728074</v>
+        <v>0.7619207642778676</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4702725186738661</v>
+        <v>0.4604792295191515</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2009250583738691</v>
+        <v>0.1912222270002815</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.4322334441420708</v>
+        <v>-0.419052434846833</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6177146581252089</v>
+        <v>-0.6045159191704457</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.509333619086746</v>
+        <v>-1.495928491433915</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.672593167470716</v>
+        <v>-1.659135873760498</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.177629097262212</v>
+        <v>-2.164176808542102</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.307427276671845</v>
+        <v>-2.293871230320242</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.40874087736649</v>
+        <v>-2.400085787562588</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.006452</t>
+          <t>X &lt; -0.006451</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2777</v>
+        <v>2778</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1816065630934389</v>
+        <v>0.1752218014828699</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6926556113351481</v>
+        <v>-0.6989243857166798</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2778181173130392</v>
+        <v>-0.2842873014566649</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2313789630020224</v>
+        <v>0.2247386276893266</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2519656610798648</v>
+        <v>0.2452489980272929</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2814795464154187</v>
+        <v>0.2747841880061017</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.03539087962585796</v>
+        <v>-0.04198647770746788</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4469011503936287</v>
+        <v>-0.4534091021455922</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2919183151936409</v>
+        <v>-0.2787195762388777</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.070049259760793</v>
+        <v>-1.056644132107962</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.202808343617619</v>
+        <v>-1.189351049907401</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.672384869497527</v>
+        <v>-1.658932580777417</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.516685556756329</v>
+        <v>-1.503129510404726</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.67922652617505</v>
+        <v>-1.673362182712395</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3157</v>
+        <v>3158</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1876897415618402</v>
+        <v>-0.1916833181882822</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.5821051401252575</v>
+        <v>-0.5861008601743052</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.517579754815074</v>
+        <v>-0.5216286426344254</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.2437975988484311</v>
+        <v>-0.247925229493049</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.3417931499972724</v>
+        <v>0.3374364103089107</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1189091914371474</v>
+        <v>0.1146435754051467</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.07508733723514638</v>
+        <v>-0.07930050500507235</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4300136125077714</v>
+        <v>-0.4341530178606448</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.1111464521563548</v>
+        <v>-0.09794771320159157</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.4547822418059937</v>
+        <v>-0.4413771141531626</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.7228467405458616</v>
+        <v>-0.7093894468356439</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.9558620773247029</v>
+        <v>-0.9599115793806092</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.9961293545140677</v>
+        <v>-0.9825733081624648</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.235585043335277</v>
+        <v>-1.231821825130353</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/drawdown/drawdown_7.xlsx
+++ b/workspaces/btc_daily_14days/drawdown/drawdown_7.xlsx
@@ -568,105 +568,105 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.1839</t>
+          <t>X ≈ -0.1837</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-12.44194402965459</v>
+        <v>-16.09597779273859</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.080193097827816</v>
+        <v>-8.613559143600483</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-14.44849912705146</v>
+        <v>-9.008832815211527</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>5.629247305796291</v>
+        <v>9.256281557471503</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>5.093683566152031</v>
+        <v>8.770526151765523</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.588366804943632</v>
+        <v>-0.02790130622253884</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.674034650773294</v>
+        <v>-9.163813954577805</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-5.14172097423512</v>
+        <v>-9.631360459274894</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-15.19162277836122</v>
+        <v>-18.75042554353625</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-16.04454707469355</v>
+        <v>-19.57814711706401</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.260365135987072</v>
+        <v>-10.70266518061711</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.2275540388829</v>
+        <v>-1.560694100366057</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-16.64666070157931</v>
+        <v>-11.04480633614295</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-6.4249820531182</v>
+        <v>-1.70752874809741</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.1774</t>
+          <t>X ≈ -0.1773</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-2.473607379632448</v>
+        <v>7.465583606725637</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>12.53756060542122</v>
+        <v>25.8307863917174</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>45.39004494495706</v>
+        <v>45.39019398375076</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>28.90537784643106</v>
+        <v>25.57985847041007</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>11.74560695593512</v>
+        <v>5.142082413989769</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>28.67965912498195</v>
+        <v>25.37688062105603</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.674002338639646</v>
+        <v>5.356814452703226</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>11.50045977693366</v>
+        <v>24.86347166646306</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-21.85004212535651</v>
+        <v>-15.11841840550903</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-56.00524093089307</v>
+        <v>-55.90612781679751</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-39.56914663471216</v>
+        <v>-36.13849547546621</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-6.227542209436976</v>
+        <v>-16.09902616554152</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-23.31167504161225</v>
+        <v>-36.49311008510063</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-6.424982053137917</v>
+        <v>-16.252983293547</v>
       </c>
     </row>
     <row r="8">
@@ -679,98 +679,98 @@
         <v>16</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>9.986505836668336</v>
+        <v>9.957494805959733</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>20.84611780539439</v>
+        <v>20.84510148517789</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>20.45698009883601</v>
+        <v>20.45698036239374</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>20.59214890863108</v>
+        <v>20.59179496571883</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>13.82418753976997</v>
+        <v>13.87270737417041</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>14.12472240655228</v>
+        <v>14.14870599619933</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>7.804511928597393</v>
+        <v>7.852473990726693</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>13.58062525204615</v>
+        <v>13.62985235053623</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.203744843805595</v>
+        <v>-5.13059821395688</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-12.29803579321239</v>
+        <v>-12.19882178960076</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-12.5056677601407</v>
+        <v>-12.40586040514287</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-12.47444623946888</v>
+        <v>-12.35082844433223</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.649084535971596</v>
+        <v>-6.500436878058856</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1645</t>
+          <t>X ≈ -0.1644</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>12</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>39.05951088322954</v>
+        <v>39.03075432565968</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>20.84569142087074</v>
+        <v>20.84467742693705</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>20.45659250046328</v>
+        <v>20.45659487021463</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>12.27901277800483</v>
+        <v>12.27860516222816</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>3.430432938424943</v>
+        <v>3.478890592476446</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>3.728425182179215</v>
+        <v>3.752353818377181</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>11.96388919403732</v>
+        <v>12.01187064926815</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>11.50023911891025</v>
+        <v>11.54945809525262</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>11.44239118393679</v>
+        <v>11.51559266323387</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>18.92117680876711</v>
+        <v>19.02047330706019</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>27.04839426952692</v>
+        <v>27.14828025603268</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>27.08936762522463</v>
+        <v>27.21303778779764</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>26.67602151000521</v>
+        <v>26.82469118597182</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>26.90835128021059</v>
+        <v>27.08035003977344</v>
       </c>
     </row>
     <row r="10">
@@ -783,1252 +783,1252 @@
         <v>13</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>1.359767079485053</v>
+        <v>1.330685699863245</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-7.915250089778183</v>
+        <v>-7.916494173951797</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.6400488653755332</v>
+        <v>-0.6402007528246401</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>14.83657992307786</v>
+        <v>14.83619058056206</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>14.30354911673293</v>
+        <v>14.35207224716053</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>14.60423655145368</v>
+        <v>14.62822372888199</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>14.52342099841111</v>
+        <v>14.57141468148161</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.30132967968315</v>
+        <v>-1.252162345447168</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.362329265199207</v>
+        <v>-1.28917104352962</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>5.472864727353254</v>
+        <v>5.572124961527024</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>12.95619146579706</v>
+        <v>13.05604914643823</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>20.68220629215329</v>
+        <v>20.8058678744224</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>20.2673136748604</v>
+        <v>20.41597901573012</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>12.80578717764647</v>
+        <v>12.97778593721313</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.1516</t>
+          <t>X ≈ -0.1515</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>18</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>19.67647154155095</v>
+        <v>19.64755275476853</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.53660652242841</v>
+        <v>12.53552811244362</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.064686353568796</v>
+        <v>1.064547196042426</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.736810673188167</v>
+        <v>6.736367918555672</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>17.2880610629425</v>
+        <v>17.33660294523896</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>23.13402130410978</v>
+        <v>23.1580556882142</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>23.05535708747624</v>
+        <v>23.10339175248744</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>17.04732606705104</v>
+        <v>17.0965675892858</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>11.44224788373431</v>
+        <v>11.51544884159913</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>5.045898436318495</v>
+        <v>5.145156951628124</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>10.39392950215377</v>
+        <v>10.49378176878344</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.6747534156199322</v>
+        <v>-0.5511209529096917</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-1.094924726414938</v>
+        <v>-0.9462740062720627</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.8694264975621451</v>
+        <v>-0.6974277380030642</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.1452</t>
+          <t>X ≈ -0.1451</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>5.193054428352639</v>
+        <v>6.72587960098118</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>3.588753086766296</v>
+        <v>5.149862763612724</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>7.031091267119059</v>
+        <v>8.451585272638702</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>7.162897920074428</v>
+        <v>8.583401772996581</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.884555410619924</v>
+        <v>-2.988454695963405</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-4.588653934014701</v>
+        <v>-6.412921461493347</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-4.674190902821827</v>
+        <v>-2.77767127058808</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-12.82254615196832</v>
+        <v>-10.63987240177988</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-1.362366504583946</v>
+        <v>0.4180571435879372</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-13.73873403276353</v>
+        <v>-11.50490824756444</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-21.63334578615597</v>
+        <v>-19.11371945995219</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-21.60442518573198</v>
+        <v>-19.06037803281228</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-22.02984356895089</v>
+        <v>-19.46015950272877</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-29.50190513004758</v>
+        <v>-26.62335366392647</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.1387</t>
+          <t>X ≈ -0.1386</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.3075321244520737</v>
+        <v>-2.503489899807889</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-10.58254608944403</v>
+        <v>-13.14528734470225</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-6.643599265768565</v>
+        <v>-9.008826365755155</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.495451187883475</v>
+        <v>4.720786445952491</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>14.63648024598769</v>
+        <v>13.30470573440476</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>6.259134305277193</v>
+        <v>9.044347385839423</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>6.176318203634139</v>
+        <v>4.448721854030332</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>14.39402979204501</v>
+        <v>13.061928483566</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>9.994571770454613</v>
+        <v>8.48871070703035</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>9.14804691443473</v>
+        <v>7.667864705849624</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>13.29026345577071</v>
+        <v>12.00775567818626</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.2910179066750942</v>
+        <v>-1.560646681313195</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.1289447695034838</v>
+        <v>-1.956084883000116</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.251069009646471</v>
+        <v>-6.252983293551964</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.1323</t>
+          <t>X ≈ -0.1321</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-7.004764821884045</v>
+        <v>-8.366413911518848</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-8.611830187477857</v>
+        <v>-9.945917759727259</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-5.986431419612465</v>
+        <v>-7.408677401555025</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.835480510349477</v>
+        <v>-4.347303256597982</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3494624758102702</v>
+        <v>-1.901654673299113</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-12.1489189373595</v>
+        <v>-10.43509861311217</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-9.21146351315393</v>
+        <v>-7.562148002858812</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-12.70590339082464</v>
+        <v>-10.96595172198894</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-6.716898399089857</v>
+        <v>-8.067979402194005</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.513173859586267</v>
+        <v>-0.07839375727183295</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-4.746183691698697</v>
+        <v>-3.221424310598032</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-13.7993139930918</v>
+        <v>-11.98315531421863</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-14.2228565812898</v>
+        <v>-15.32167133764082</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-17.03104265918198</v>
+        <v>-15.07651270532347</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.1258</t>
+          <t>X ≈ -0.1257</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>24</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-14.93262304896543</v>
+        <v>-10.80890442968327</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-4.079916214752508</v>
+        <v>-4.081087525417217</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>3.834637124224891</v>
+        <v>3.834555461230323</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.121418624446953</v>
+        <v>8.121019222229762</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>3.429713294964976</v>
+        <v>3.478196897309601</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>12.04433562939371</v>
+        <v>7.910104838325999</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7.803750659154652</v>
+        <v>3.692450797618207</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9812002296727513</v>
+        <v>-5.092349371498273</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-17.68758557604988</v>
+        <v>-17.6144681143708</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-18.54117597707231</v>
+        <v>-22.60441367923528</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-14.5870614798696</v>
+        <v>-14.48727182730981</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-18.72093542513097</v>
+        <v>-18.5973362429995</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-31.64258877063986</v>
+        <v>-27.3283532369463</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-27.25831538645609</v>
+        <v>-27.08631662688753</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.1193</t>
+          <t>X ≈ -0.1192</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>3.915090631901883</v>
+        <v>2.742733764532211</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-5.357805598415567</v>
+        <v>-4.080893155981947</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-10.86734574899459</v>
+        <v>-9.72368522889721</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-10.74044366763142</v>
+        <v>-9.59682308693715</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-13.83795264419168</v>
+        <v>-12.71245736750067</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-5.867748475320937</v>
+        <v>-4.56443474457064</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-5.953637586753146</v>
+        <v>-4.625980838940691</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.301192775451241</v>
+        <v>0.1628057702744456</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-9.04453876243484</v>
+        <v>-7.758387065908707</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-12.45741165371955</v>
+        <v>-11.21227946078319</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-12.66529203841539</v>
+        <v>-14.04883698536909</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-17.75973700418957</v>
+        <v>-19.25473976484665</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-13.05751640074705</v>
+        <v>-14.39297861762677</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-12.83523846337916</v>
+        <v>-14.14772013566136</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.1129</t>
+          <t>X ≈ -0.1128</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>48</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-10.77883115691431</v>
+        <v>-10.80801818455135</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>2.151036094239259</v>
+        <v>2.149873242263709</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-4.474814181578004</v>
+        <v>-4.474999302499597</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-8.502109413755129</v>
+        <v>-8.502660290177587</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.35134307137136</v>
+        <v>1.399778332992561</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.648835580876515</v>
+        <v>1.672749830738447</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5146404255527131</v>
+        <v>-0.4667261123424211</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-5.141271210436201</v>
+        <v>-5.092129908998075</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>7.280524655651838</v>
+        <v>7.353703856895137</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>2.271057658310106</v>
+        <v>2.370297971934164</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.01474238905721137</v>
+        <v>0.08508013216266619</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>2.101873394857869</v>
+        <v>2.225502314494122</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4004937517130287</v>
+        <v>-0.2518470737618799</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.1749820531227542</v>
+        <v>-0.002983293556091837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.1065</t>
+          <t>X ≈ -0.1064</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>44</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.056641215967325</v>
+        <v>2.027579754524226</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>2.717251835415283</v>
+        <v>2.716095254180047</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-9.006776261862306</v>
+        <v>-9.007001218623934</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-8.87938189892806</v>
+        <v>-8.879938530134318</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-11.68586371052636</v>
+        <v>-11.63752086553532</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-11.39181276155786</v>
+        <v>-11.36797934385454</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-16.01619052258476</v>
+        <v>-15.96836191159309</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-11.94844280246271</v>
+        <v>-11.89933599983758</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-7.472894893891613</v>
+        <v>-7.399773576261772</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-3.783186197641179</v>
+        <v>-3.683966936052833</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-6.259777140267765</v>
+        <v>-6.159971101532278</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.955546889621843</v>
+        <v>-3.831928859711276</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.37670827986603</v>
+        <v>-4.228065714928796</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.152254780395481</v>
+        <v>-3.980256020828818</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.09998</t>
+          <t>X ≈ -0.09995</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>45</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.063048187955189</v>
+        <v>3.034000728122976</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-9.617035973947424</v>
+        <v>-9.618307403902975</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.065156360755765</v>
+        <v>1.06501491033768</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.19517498695361</v>
+        <v>1.194694416236274</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.774998434292165</v>
+        <v>-3.726606380739106</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-3.478911359362272</v>
+        <v>-3.455032814605154</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.8720334224018771</v>
+        <v>0.9199485279705826</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.405887365678069</v>
+        <v>0.4550477697019346</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>2.564404774145039</v>
+        <v>2.637561623715783</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5037695609229615</v>
+        <v>-0.404543325639807</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.928998039938193</v>
+        <v>-2.829186924105187</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-7.337518180267907</v>
+        <v>-7.213907502198182</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-9.981236560176626</v>
+        <v>-9.832599614113235</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-11.98053760867831</v>
+        <v>-11.80853884911064</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.09354</t>
+          <t>X ≈ -0.09348</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7551840496930566</v>
+        <v>0.03109160071620209</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-2.360186298048525</v>
+        <v>-1.545811674466336</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.035931492589917</v>
+        <v>-0.2494269312901309</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-2.625946828867939</v>
+        <v>-1.810435977129856</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>3.716476149809054</v>
+        <v>4.464550320229101</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4.014561844577514</v>
+        <v>4.738308370008255</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>3.93130377006991</v>
+        <v>4.679245843317069</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>1.744688022638023</v>
+        <v>2.523230838144443</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.03750368444154617</v>
+        <v>0.7943999377104447</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-4.33099460810633</v>
+        <v>-3.414435412797182</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-6.259538552004187</v>
+        <v>-5.312968959355459</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.057295395852407</v>
+        <v>-0.1742997158130564</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.2459437370288811</v>
+        <v>1.124955967903567</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.252568260019309</v>
+        <v>-0.3207799037263541</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ -0.0871</t>
+          <t>X ≈ -0.08704</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>7.784066490859288</v>
+        <v>7.164531943464347</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>6.181639813254741</v>
+        <v>5.589812173489562</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>11.65364719635706</v>
+        <v>11.15026889631</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>11.78664680389813</v>
+        <v>11.28278479214855</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>9.786195691753825</v>
+        <v>9.309179869670608</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>5.683986937142279</v>
+        <v>5.116577858868716</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4.133502523442694</v>
+        <v>3.568020739374099</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.7320860200231536</v>
+        <v>0.1238408662160424</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.14001863576636</v>
+        <v>1.577506300576253</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.1772086383002716</v>
+        <v>-0.7357476127836904</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3818865933925366</v>
+        <v>-0.9400123875379336</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.3477198323140627</v>
+        <v>-0.8822182800767067</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.7679700381612804</v>
+        <v>-1.277622519047227</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9279591233478328</v>
+        <v>0.4634346168916679</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ -0.08064</t>
+          <t>X ≈ -0.08058</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>72</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-8.008666527363296</v>
+        <v>-8.037819790123692</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-10.99938980625963</v>
+        <v>-11.00068628375188</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-11.39694425898359</v>
+        <v>-11.39720011333776</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-12.65530907013213</v>
+        <v>-12.65590580746429</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.7272260015467324</v>
+        <v>-0.6788232458529251</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-7.358880873815487</v>
+        <v>-7.335036300063486</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-6.059033947674862</v>
+        <v>-6.011169794435403</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-3.753798535052454</v>
+        <v>-3.70466881476775</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.815710223606153</v>
+        <v>-3.742591347821332</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.278246826654595</v>
+        <v>-3.179043808680717</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-9.034644070148893</v>
+        <v>-8.934860168024095</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-4.838622770681688</v>
+        <v>-4.715017374351881</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-5.260147322299126</v>
+        <v>-5.111512148155505</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-5.036093164233868</v>
+        <v>-4.864094404667206</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ -0.07419</t>
+          <t>X ≈ -0.07414</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>82</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-2.472718545595733</v>
+        <v>-2.501807874761717</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>1.999087344819721</v>
+        <v>1.997923793525977</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.041752816248582</v>
+        <v>-2.041923675840721</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6.59940240572594</v>
+        <v>6.598972901917406</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>6.064057590815096</v>
+        <v>6.112509945356237</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.279976999343603</v>
+        <v>0.3038703425910683</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>3.846894072687292</v>
+        <v>3.894813640799619</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>3.381792321065092</v>
+        <v>3.430955196191015</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3.321903323550266</v>
+        <v>3.395048042526895</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>3.692184207636927</v>
+        <v>3.791405844852555</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>4.707161396791321</v>
+        <v>4.806976541304657</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>4.742683231905986</v>
+        <v>4.866301763851119</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>5.543031212587103</v>
+        <v>5.691673669138595</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>3.331115507853134</v>
+        <v>3.503114267419512</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ -0.06773</t>
+          <t>X ≈ -0.0677</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>105</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>3.69426262678703</v>
+        <v>4.078766438575578</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>12.53008028204025</v>
+        <v>11.94504877146012</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.59627198394876</v>
+        <v>3.94896360712432</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.82743351253476</v>
+        <v>2.188726054805379</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>6.039965317183153</v>
+        <v>5.494062391631715</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>8.240016611441732</v>
+        <v>9.565824470687204</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>5.306840939993776</v>
+        <v>6.651460289028734</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.940930855673741</v>
+        <v>3.842930325650286</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>5.733852330154242</v>
+        <v>6.659787808320019</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.033102491717365</v>
+        <v>2.547792377375941</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>5.635285908385043</v>
+        <v>5.735099247868639</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>3.767524344856966</v>
+        <v>3.891137054713887</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.396391733510256</v>
+        <v>2.545028740901955</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>5.479779851638931</v>
+        <v>5.651778611205813</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ -0.06128</t>
+          <t>X ≈ -0.06125</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>112</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.973959130737136</v>
+        <v>1.483512481014948</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-4.967521383636793</v>
+        <v>-4.563420345908987</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2.646310038234155</v>
+        <v>2.166082812675882</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8.117085887834897</v>
+        <v>8.537362015256519</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.4590812534481259</v>
+        <v>0.91733398589232</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>1.64786361285104</v>
+        <v>2.081323381229524</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.890437372785314</v>
+        <v>-2.440336015527478</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.357244641823307</v>
+        <v>-2.911163906431078</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-4.310696959803167</v>
+        <v>-4.240268692691949</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-2.485247098066623</v>
+        <v>-2.386927693957233</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-5.366719999724381</v>
+        <v>-5.266946499126576</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-2.657203113325501</v>
+        <v>-2.533609027975338</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.185559415707672</v>
+        <v>-2.036930602122389</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-1.067839195980106</v>
+        <v>-0.8958404364132306</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ -0.05484</t>
+          <t>X ≈ -0.0548</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>121</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.054089313470385</v>
+        <v>2.028244604281959</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.018607606581639</v>
+        <v>-2.022247660746025</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>5.822089365215597</v>
+        <v>5.829841153304422</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>3.481247351162708</v>
+        <v>3.48606368597418</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.473563641411971</v>
+        <v>0.5235364445351678</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.7716732801488746</v>
+        <v>0.796855233101688</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.811126243400466</v>
+        <v>4.86516756915902</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>1.872236059909717</v>
+        <v>1.922993751830241</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>5.112400819922833</v>
+        <v>5.188694795060357</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>1.789340183472433</v>
+        <v>1.888967945519148</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>3.236668302191887</v>
+        <v>3.336459516313219</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.03182595843330915</v>
+        <v>0.09176590893745384</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.374191533530599</v>
+        <v>0.5228184830426628</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2266349456843599</v>
+        <v>-0.05463618611807419</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ -0.04838</t>
+          <t>X ≈ -0.04836</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-4.38983757587679</v>
+        <v>-4.994825539998793</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-4.760435249495131</v>
+        <v>-5.348227063530452</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-2.63178029000413</v>
+        <v>-3.26384339631332</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-7.207634358426596</v>
+        <v>-8.093370917228626</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-9.012740020579635</v>
+        <v>-9.828494130857074</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-7.455897733083873</v>
+        <v>-8.318373872614472</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-7.197227902881565</v>
+        <v>-8.382866586613261</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-10.19166491638425</v>
+        <v>-10.71504193352504</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-9.624371723864677</v>
+        <v>-10.1309616034892</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-11.10789461195679</v>
+        <v>-11.58238753755486</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-8.787144459015423</v>
+        <v>-9.305323121356828</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-11.28581270332813</v>
+        <v>-11.9990163950516</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-9.811702045850055</v>
+        <v>-10.53550604110001</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-9.589539015148212</v>
+        <v>-10.29025037430144</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ -0.04194</t>
+          <t>X ≈ -0.0419</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>170</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>3.082442828894628</v>
+        <v>3.338324561780738</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>3.225754628739644</v>
+        <v>3.496707511593613</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.659710812193502</v>
+        <v>2.519320475647177</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.5556605606809697</v>
+        <v>0.3021466566205362</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.59767370168619</v>
+        <v>4.508048296121821</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.65204370811221</v>
+        <v>-1.364552786151989</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-2.322922989714023</v>
+        <v>-2.279531633501207</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.027993107916721</v>
+        <v>-0.9812696624306838</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.5025575149105421</v>
+        <v>-0.4305000973493236</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.9986794054942507</v>
+        <v>1.097894098084936</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.2065169628394088</v>
+        <v>0.3060597101523896</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.9348874047557558</v>
+        <v>-0.8112820178303366</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>2.760527586728379</v>
+        <v>2.909162665681578</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.810312064524176</v>
+        <v>1.982310824091101</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ -0.03549</t>
+          <t>X ≈ -0.03546</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>211</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.237394607640489</v>
+        <v>-2.269059175965829</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.369284734427566</v>
+        <v>-3.375720545243603</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.431142519321966</v>
+        <v>1.434062479164439</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.1437485779513636</v>
+        <v>0.1444623493617172</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.8656296774909933</v>
+        <v>-0.8177521807045451</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.03973962466528</v>
+        <v>-1.018201573690106</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-3.014268564545816</v>
+        <v>-2.972904169062431</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-2.534945889925176</v>
+        <v>-2.490938875122659</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.543488441672089</v>
+        <v>-3.475156109118593</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.553794692644338</v>
+        <v>-1.456586699999818</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-2.706046347044257</v>
+        <v>-2.607695057662717</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.672921667137437</v>
+        <v>-2.549334619985579</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-3.568287459891671</v>
+        <v>-3.419667783466508</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-1.922612384876089</v>
+        <v>-2.224547274598855</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ -0.02903</t>
+          <t>X ≈ -0.02901</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.889745645576944</v>
+        <v>2.549039131569266</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>3.584775289543934</v>
+        <v>2.986334626950899</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>5.767162958909353</v>
+        <v>5.131157386686532</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.382919059716542</v>
+        <v>4.756213782407471</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>5.63400938146026</v>
+        <v>4.774158583856931</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>4.901723738080179</v>
+        <v>4.029799946057764</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.78745548995785</v>
+        <v>2.952179780665489</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.5221387105810678</v>
+        <v>-0.5620240819094917</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.082340699720966</v>
+        <v>-2.120841196282626</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.93112521186908</v>
+        <v>-2.950072190619068</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-1.62199154747244</v>
+        <v>-2.140850171002228</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-1.588624988229661</v>
+        <v>-2.083943996792314</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-4.071008815152481</v>
+        <v>-4.722734259588769</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2394150428135973</v>
+        <v>-0.9230340549774141</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ -0.02258</t>
+          <t>X ≈ -0.02257</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.040633966970205</v>
+        <v>-2.51358390391465</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.793516464643382</v>
+        <v>-2.246890620191465</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.617291300432058</v>
+        <v>-2.267751175818404</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-3.975140069160766</v>
+        <v>-3.624865712003178</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.256043105786496</v>
+        <v>-4.860797786574224</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1.608189630416028</v>
+        <v>-1.244623434499594</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.5750059032988943</v>
+        <v>-0.192218223590956</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.8216358362421303</v>
+        <v>1.196324404398055</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.845103877166601</v>
+        <v>-1.443034426263885</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.204283939906091</v>
+        <v>-0.784546307110304</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.40989557715843</v>
+        <v>-0.9896211841693514</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.867775638875791</v>
+        <v>-2.419533462165091</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.425177561748946</v>
+        <v>-0.9578241882952057</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.559310411331801</v>
+        <v>-3.836626416232669</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ -0.01613</t>
+          <t>X ≈ -0.01612</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.366875456348218</v>
+        <v>2.211852121557804</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.9446186866509763</v>
+        <v>-1.0821186032124</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.058326317977389</v>
+        <v>-1.191755250890232</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1.635566143875934</v>
+        <v>1.229172998255663</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>2.238658404976512</v>
+        <v>1.887132357206113</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>3.39122846159021</v>
+        <v>3.019516729893262</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.877769231867887</v>
+        <v>3.531926543246563</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>3.414382049866909</v>
+        <v>3.066093782863192</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.925636113739088</v>
+        <v>3.602187076305199</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.229259150559912</v>
+        <v>-0.08697101740376922</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.2610882843373332</v>
+        <v>-0.577644416229262</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.227373686406338</v>
+        <v>-0.5194776788642983</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-1.505573679167576</v>
+        <v>-1.774234459296387</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.424982053122626</v>
+        <v>-2.671321402438608</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ -0.009676</t>
+          <t>X ≈ -0.009669</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>368</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.885726249839237</v>
+        <v>-3.047379125330202</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-2.327980159404646</v>
+        <v>-2.456017321734691</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-7.056221518774265</v>
+        <v>-7.195625450939339</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-3.676919252447426</v>
+        <v>-3.540146925018021</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.131597178979369</v>
+        <v>-2.944218085051332</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.9386962348156374</v>
+        <v>-0.7692586531888992</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-1.56450442192434</v>
+        <v>-1.373393003283951</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.6766068866226504</v>
+        <v>-0.4805301114933442</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.851879850880707</v>
+        <v>1.928149453282863</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.821364501677046</v>
+        <v>1.919538263772253</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>1.888448004831744</v>
+        <v>1.987136946670958</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.65201014553724</v>
+        <v>1.773564553601055</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.675119423162776</v>
+        <v>3.824058800950247</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.085887512094573</v>
+        <v>3.257886271661306</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ -0.003226</t>
+          <t>X ≈ -0.003223</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="C34" s="4" t="inlineStr"/>
       <c r="D34" s="4" t="inlineStr"/>
@@ -2182,677 +2182,677 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.1871</t>
+          <t>X &gt; -0.187</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4089</v>
+        <v>4100</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.2137292923578542</v>
+        <v>-0.2125188270751721</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.03211675417608717</v>
+        <v>-0.03200486335023101</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-0.2185808254263861</v>
+        <v>-0.2179926001332717</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.1239086721569009</v>
+        <v>-0.1235662148070915</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.06331273484444466</v>
+        <v>-0.06420655151410415</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1009960336686078</v>
+        <v>0.1002007261769222</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1272960650083661</v>
+        <v>0.12590300247507</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.03991229797681939</v>
+        <v>0.03872590832917666</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.06568863075283105</v>
+        <v>0.06390648341582761</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03776644369123261</v>
+        <v>-0.03984388725748289</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.03327344813900623</v>
+        <v>-0.03537574287751966</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.08292568650617227</v>
+        <v>-0.08541727922703757</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.09815046618547996</v>
+        <v>-0.1011503208969913</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.07868711548518803</v>
+        <v>-0.08225158623901052</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.1806</t>
+          <t>X &gt; -0.1805</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4079</v>
+        <v>4089</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.1837508301433459</v>
+        <v>-0.1697900306402715</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.02219256603279263</v>
+        <v>-0.008919244107694624</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-0.1836950242456368</v>
+        <v>-0.1943439715282693</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-0.1380130015953824</v>
+        <v>-0.1487993587286169</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-0.07595553038501635</v>
+        <v>-0.08797325724558647</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.1124923877716029</v>
+        <v>0.100545339127855</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1390669174618608</v>
+        <v>0.1508936814986868</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.05261549305455304</v>
+        <v>0.0647398359505118</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.1030931696327357</v>
+        <v>0.1145197512799641</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.001475479895439946</v>
+        <v>0.01271696760382923</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.0180072267910063</v>
+        <v>-0.006679195111530589</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.06786163072688112</v>
+        <v>-0.08144857171112818</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.05758044844732524</v>
+        <v>-0.07171030716069993</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.0631286576827037</v>
+        <v>-0.07787935616308772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.1742</t>
+          <t>X &gt; -0.1741</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4073</v>
+        <v>4084</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.1803776066479088</v>
+        <v>-0.1791379415577126</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.04069453485889341</v>
+        <v>-0.0405545350428369</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-0.250830413348325</v>
+        <v>-0.2501526614833054</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-0.1807972748799713</v>
+        <v>-0.1802986949542955</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-0.09337005896785655</v>
+        <v>-0.09437636164230412</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.07040964767259794</v>
+        <v>0.06959977683362695</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1461571250573925</v>
+        <v>0.1445201252166086</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.03575149460052529</v>
+        <v>0.03437899874370487</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1354326765735436</v>
+        <v>0.1331692837931726</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.08397984976156181</v>
+        <v>0.08117784515572879</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.040256175233921</v>
+        <v>0.03755662305736962</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.05878770893158247</v>
+        <v>-0.06183841305070814</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.02332447801791915</v>
+        <v>-0.02711995483706175</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.05375691194916499</v>
+        <v>-0.05807633958939817</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.1677</t>
+          <t>X &gt; -0.1676</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4057</v>
+        <v>4068</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.2204737700920916</v>
+        <v>-0.2190067035931804</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.123067962870735</v>
+        <v>-0.1227006747487209</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-0.332497893800614</v>
+        <v>-0.3315966458446695</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-0.2627216374474273</v>
+        <v>-0.2619981783787679</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-0.1482581342894775</v>
+        <v>-0.1493108109473695</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.01498223723579173</v>
+        <v>0.01422472778990169</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.1159540989650552</v>
+        <v>0.1142036891674039</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.0176667898754701</v>
+        <v>-0.01909385613060266</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.156489329352965</v>
+        <v>0.1538724007951444</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.1328120534311665</v>
+        <v>0.1294767621065915</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.08973480056446448</v>
+        <v>0.08649828295196471</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.009822824413809883</v>
+        <v>-0.01350413564153996</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.002806200051409746</v>
+        <v>-0.001659514627739611</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.02863006889795372</v>
+        <v>-0.03371092384124807</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.1613</t>
+          <t>X &gt; -0.1612</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4045</v>
+        <v>4056</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.3370027727719105</v>
+        <v>-0.3351302569341712</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.1852744183972916</v>
+        <v>-0.1847343377714523</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-0.3941713387279719</v>
+        <v>-0.3931001710401105</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.2999282661212064</v>
+        <v>-0.299100555126131</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.1588747703519218</v>
+        <v>-0.1600451346261451</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.003965842837949651</v>
+        <v>0.003165174267458326</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.08080571302169659</v>
+        <v>0.07900349106058968</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.05183610283108209</v>
+        <v>-0.05332034119386009</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1230082855321868</v>
+        <v>0.1202578438056818</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.07707401212979903</v>
+        <v>0.07358623978424816</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.009758554921056373</v>
+        <v>0.006433839244628814</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.0902159728428984</v>
+        <v>-0.0940560348233106</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.07632323968146437</v>
+        <v>-0.08102741610880315</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1085420036789913</v>
+        <v>-0.1139300391182232</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.1548</t>
+          <t>X &gt; -0.1547</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4032</v>
+        <v>4043</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-0.3424735089027067</v>
+        <v>-0.3404865783386626</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.1603513817584101</v>
+        <v>-0.1598733736679847</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-0.3933785788454287</v>
+        <v>-0.392305635407368</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.3487314919296338</v>
+        <v>-0.3477670861090516</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-0.205504609273568</v>
+        <v>-0.206707891480761</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.04310844268090364</v>
+        <v>-0.04386073748370478</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.03423974111940709</v>
+        <v>0.03240409816535106</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.04780747770729477</v>
+        <v>-0.04946554375252532</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.1277973202939719</v>
+        <v>0.124789769488423</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.05967686944678974</v>
+        <v>0.05590605096835333</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.03198341626976742</v>
+        <v>-0.03552633859200682</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1571905485980949</v>
+        <v>-0.1612583625057766</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.1419153229872734</v>
+        <v>-0.1469341892015308</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.1501804658211583</v>
+        <v>-0.1560255888813487</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.1484</t>
+          <t>X &gt; -0.1483</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4014</v>
+        <v>4025</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-0.4322445629406104</v>
+        <v>-0.4298740834308106</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.2172884127188937</v>
+        <v>-0.2166478399412739</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.3999169866140946</v>
+        <v>-0.3988207536598125</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.3805052236117845</v>
+        <v>-0.3794476898566188</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.283951092108623</v>
+        <v>-0.2851624492598788</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.147041759931092</v>
+        <v>-0.1476208606296865</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.06899396895395427</v>
+        <v>-0.07077050500925708</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.1244672693878286</v>
+        <v>-0.1261434559002836</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.07705987382114898</v>
+        <v>0.07385017612246969</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.03731713147875126</v>
+        <v>0.03314666805857769</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.07873638899811652</v>
+        <v>-0.08261392764362085</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1548696388805055</v>
+        <v>-0.1595148776294408</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1376417382185338</v>
+        <v>-0.1433595018208393</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1469551472931627</v>
+        <v>-0.1536044115685087</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.1419</t>
+          <t>X &gt; -0.1418</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3988</v>
+        <v>3998</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.4689190297845443</v>
+        <v>-0.4781995835506621</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.2421021235981868</v>
+        <v>-0.2528899075490685</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-0.448363880946367</v>
+        <v>-0.4585908794001909</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.429684883023981</v>
+        <v>-0.4399771884801922</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.2539571823088949</v>
+        <v>-0.2669060984192058</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.1180844087459931</v>
+        <v>-0.1053089256063515</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.03897011732892963</v>
+        <v>-0.05248978448133812</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.04168139904001578</v>
+        <v>-0.05514028392961023</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.08644429855497293</v>
+        <v>0.07152561681242275</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.1271309053679914</v>
+        <v>0.1110674991545721</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.06179015170551594</v>
+        <v>0.04591029681168379</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.01502800291807915</v>
+        <v>-0.03187022900763736</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.005085756164376676</v>
+        <v>-0.01290587500130869</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.04442617155126527</v>
+        <v>0.02515577597868202</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.1355</t>
+          <t>X &gt; -0.1354</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3965</v>
+        <v>3976</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.4698551959440991</v>
+        <v>-0.4669932488027513</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1821197248051263</v>
+        <v>-0.181553704425987</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.4124268282727428</v>
+        <v>-0.41128072328857</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.4698559119346655</v>
+        <v>-0.4685327216687014</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3403329858021706</v>
+        <v>-0.3420005300897628</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1550771024212878</v>
+        <v>-0.1559357965449308</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.07502349220462889</v>
+        <v>-0.07739588509684125</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.1254194463022955</v>
+        <v>-0.1277196382769219</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.02896966252630762</v>
+        <v>0.02495165504561925</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.07480276710607114</v>
+        <v>0.06925423493241567</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-0.02027697642530057</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.01680330075430447</v>
+        <v>-0.02341120437213817</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.005863234623483038</v>
+        <v>-0.002153878478175386</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.06934329366161762</v>
+        <v>0.05989397002539221</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.129</t>
+          <t>X &gt; -0.1289</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3932</v>
+        <v>3942</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4150098201414565</v>
+        <v>-0.3988602446088549</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1113719004744524</v>
+        <v>-0.09733544519711046</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.365646016595683</v>
+        <v>-0.350927733166543</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4500019923650527</v>
+        <v>-0.4350780798149216</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.3402563649552022</v>
+        <v>-0.3285484141919639</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.05441668010364253</v>
+        <v>-0.0672773653518064</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.001655683963058152</v>
+        <v>-0.01283942340128874</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.01983552713413417</v>
+        <v>-0.03423919919873697</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.08558554402003438</v>
+        <v>0.09475369866463978</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.08813013960883609</v>
+        <v>0.07052770822895127</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.02476274856178406</v>
+        <v>0.00733312234737582</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.09886883883041264</v>
+        <v>0.07974234705727667</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.1252802625800271</v>
+        <v>0.1299779311645253</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.212861283601562</v>
+        <v>0.1904464375448782</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.1226</t>
+          <t>X &gt; -0.1225</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3908</v>
+        <v>3918</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3258535464741641</v>
+        <v>-0.3350927457722577</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.08700008278185578</v>
+        <v>-0.07293267594614861</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.3914410000602899</v>
+        <v>-0.3765662213404823</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.5026412182615445</v>
+        <v>-0.4874890893220893</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3634086863057888</v>
+        <v>-0.3518669153343978</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.1287181272448805</v>
+        <v>-0.1161434125412626</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.046258921821142</v>
+        <v>-0.03553645385163406</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.01393154738465796</v>
+        <v>-0.003255369659370899</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.194735008421695</v>
+        <v>0.2032328521901192</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.2025373419630583</v>
+        <v>0.2094247458244496</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1144975954098726</v>
+        <v>0.09612090151831865</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.2144459376879055</v>
+        <v>0.1941501791556277</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3203746476356244</v>
+        <v>0.2981759781361148</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3815686121791941</v>
+        <v>0.3575322756118524</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.1161</t>
+          <t>X &gt; -0.116</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3869</v>
+        <v>3880</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.3686027899367232</v>
+        <v>-0.3652364074711159</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.03386970927198263</v>
+        <v>-0.0336794547499224</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.285842580518171</v>
+        <v>-0.2850222722974038</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3994428994387391</v>
+        <v>-0.3982739625413174</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2275836115170762</v>
+        <v>-0.2308095861636943</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.07086798933456606</v>
+        <v>-0.0725776726914944</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.01328818800887888</v>
+        <v>0.00942150662088892</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.0009557945041720473</v>
+        <v>-0.00488174164841837</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2878680342845499</v>
+        <v>0.2812074802539684</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.3301511984716257</v>
+        <v>0.321286797332462</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.2433194604187179</v>
+        <v>0.2346539942249564</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.3956279316742695</v>
+        <v>0.3846289981948345</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.4552254491054981</v>
+        <v>0.4420584200533852</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.5147956672184222</v>
+        <v>0.4995940260315379</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.1097</t>
+          <t>X &gt; -0.1096</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3821</v>
+        <v>3832</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.2378278719532361</v>
+        <v>-0.2344291200755393</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.06131683792116149</v>
+        <v>-0.06103084552670879</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.2332200636768107</v>
+        <v>-0.2325382176393447</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.2976559345899688</v>
+        <v>-0.2967576411095507</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.2474183356151229</v>
+        <v>-0.2512344870299543</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.09247117472324362</v>
+        <v>-0.09443981260918832</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.01992010987513737</v>
+        <v>0.01538577742210379</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.06361765222828808</v>
+        <v>0.05884161744155136</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.2000251874314714</v>
+        <v>0.1926167114442734</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3057692277644151</v>
+        <v>0.2956206865858846</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2465612737594256</v>
+        <v>0.2365275707852277</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3741938091323149</v>
+        <v>0.3615700422495394</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.4659751276292567</v>
+        <v>0.4507503469070144</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.5234607628939969</v>
+        <v>0.5058893578009034</v>
       </c>
     </row>
     <row r="19">
@@ -2862,829 +2862,829 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3777</v>
+        <v>3788</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2645571914842151</v>
+        <v>-0.2607037743739582</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.09368565487292813</v>
+        <v>-0.0932889100428369</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1310128958928161</v>
+        <v>-0.1306173168887312</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1976834849127371</v>
+        <v>-0.1970586022718734</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.1141666553143281</v>
+        <v>-0.118975616741082</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.03916002194625889</v>
+        <v>0.03650943220992531</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2067320950030833</v>
+        <v>0.2010470494169994</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2035516368738897</v>
+        <v>0.1977433637879855</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.2894105418339663</v>
+        <v>0.2808070949339907</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.3534033391538358</v>
+        <v>0.341846097197319</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3223565849103878</v>
+        <v>0.3108269217836366</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.4246329382679122</v>
+        <v>0.4102801667707254</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.5223897609175197</v>
+        <v>0.5050977351648811</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.5779303111875436</v>
+        <v>0.5579987550183532</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.09677</t>
+          <t>X &gt; -0.0967</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3732</v>
+        <v>3743</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.3046810505610509</v>
+        <v>-0.3003141678049843</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.02114573964967548</v>
+        <v>0.02122507131535656</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.1454361586337427</v>
+        <v>-0.1449917358642026</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.2144784021780097</v>
+        <v>-0.2137908720642585</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.07002479302762055</v>
+        <v>-0.07560308551482109</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.08158049680126567</v>
+        <v>0.07848629598407797</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.1987099728881461</v>
+        <v>0.1924040981653548</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2011118973786594</v>
+        <v>0.1946499365194541</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.2619789393543215</v>
+        <v>0.2524731505591191</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3637390252480088</v>
+        <v>0.3508195206618225</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.3615610217051923</v>
+        <v>0.3485775557844377</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.5182280080251829</v>
+        <v>0.5019415199910355</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6490412036959867</v>
+        <v>0.6293821008387965</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.7293587828901096</v>
+        <v>0.7066747347634319</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; -0.09032</t>
+          <t>X &gt; -0.09026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3674</v>
+        <v>3684</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.2975691360401882</v>
+        <v>-0.3056216977568766</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.05873889647778441</v>
+        <v>0.04632147956755972</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1313782573355837</v>
+        <v>-0.1433191852316966</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1764094939722369</v>
+        <v>-0.1882202799907304</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.1298008013794174</v>
+        <v>-0.1483145542821589</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.01949205962896627</v>
+        <v>0.003858309456546749</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.139784975545588</v>
+        <v>0.1205464263510336</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1767440652433621</v>
+        <v>0.1573572456410872</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.2667067543189887</v>
+        <v>0.2437940842067974</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.4378529476036306</v>
+        <v>0.4111208347427393</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.4660857291834475</v>
+        <v>0.439248360451451</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.543100179343881</v>
+        <v>0.5127716592180818</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.6554047456303067</v>
+        <v>0.6214453858125282</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.7606466893922175</v>
+        <v>0.7231296271822387</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; -0.08387</t>
+          <t>X &gt; -0.08381</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3606</v>
+        <v>3617</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.449968254905734</v>
+        <v>-0.4439961224076399</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.05672346135384032</v>
+        <v>-0.05636413737819623</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3536139009437633</v>
+        <v>-0.3525175268029699</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.4020023470657463</v>
+        <v>-0.4007050297372956</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.3167913065189225</v>
+        <v>-0.3235017609188304</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.08732592475009682</v>
+        <v>-0.09084785858620137</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.06447360747653619</v>
+        <v>0.0566866588717545</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.1662717266618259</v>
+        <v>0.1579780909331774</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2313808508418873</v>
+        <v>0.219088881415324</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4494514467277213</v>
+        <v>0.4323650111276649</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4820763331588154</v>
+        <v>0.4647972877711268</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.5598987818931676</v>
+        <v>0.5386119483894305</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6822459783806778</v>
+        <v>0.6566230329304688</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7574916018966604</v>
+        <v>0.7279401236404794</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; -0.07742</t>
+          <t>X &gt; -0.07736</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3534</v>
+        <v>3545</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.29597100657044</v>
+        <v>-0.2897633144878782</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.1662171093403444</v>
+        <v>0.1659182870333495</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1286224505252989</v>
+        <v>-0.1281967521258238</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.1523594257129446</v>
+        <v>-0.1517982720514439</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3084293093366952</v>
+        <v>-0.3162850763165039</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.06082120494223631</v>
+        <v>0.05628375432955579</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.1892309770212179</v>
+        <v>0.1799266206878727</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2461373347103333</v>
+        <v>0.2364295936723764</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3138343192516899</v>
+        <v>0.2995517802884038</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.5253977612957854</v>
+        <v>0.5057137939277183</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.6759653736336801</v>
+        <v>0.6557071147999665</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.6698856386519054</v>
+        <v>0.6453147160163297</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.8033134140481692</v>
+        <v>0.7737755669327697</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.8755272847380269</v>
+        <v>0.841516001225294</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; -0.07096</t>
+          <t>X &gt; -0.07092</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3452</v>
+        <v>3463</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2442637938821193</v>
+        <v>-0.2373845521597104</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.1226784768637188</v>
+        <v>0.1225384280866564</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.0831772912004638</v>
+        <v>-0.08288182063733274</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3127431076880285</v>
+        <v>-0.3116490477561626</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.4598035636276663</v>
+        <v>-0.4685118137629871</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.0556153025259789</v>
+        <v>0.05042117845966487</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.1023455848298482</v>
+        <v>0.0919622153603612</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.1716519034006296</v>
+        <v>0.1607867697028382</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.2423796094160977</v>
+        <v>0.2262538612865086</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.4501728225356558</v>
+        <v>0.4279122495512198</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.580206951299111</v>
+        <v>0.5574096579783188</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.5731389982559492</v>
+        <v>0.5453664232290194</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6907245208036201</v>
+        <v>0.6573251931583357</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8171963941541804</v>
+        <v>0.7784923056353605</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; -0.06451</t>
+          <t>X &gt; -0.06447</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3347</v>
+        <v>3358</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.3678207924391117</v>
+        <v>-0.3723446039843736</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.2665588071349489</v>
+        <v>-0.2471350638889902</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.1986066828618576</v>
+        <v>-0.2089520320473852</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3798833960427928</v>
+        <v>-0.3898323073657437</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.6637102658939256</v>
+        <v>-0.6549532347178513</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.2011406393432011</v>
+        <v>-0.2471122776701407</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.06092660288817342</v>
+        <v>-0.1131441865857923</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.0847758083935588</v>
+        <v>0.04565125053235164</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.07010454647092246</v>
+        <v>0.02508618277592944</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4005141385607232</v>
+        <v>0.3616265397770704</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.4216221617879015</v>
+        <v>0.3955104897417243</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.4729267301373028</v>
+        <v>0.4407488186114108</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.6372153910354186</v>
+        <v>0.5982993228447313</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.6709247290702507</v>
+        <v>0.62611140566964</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; -0.05806</t>
+          <t>X &gt; -0.05802</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3235</v>
+        <v>3246</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4488963261008578</v>
+        <v>-0.4363791059929767</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.1038052341617757</v>
+        <v>-0.09820593524258925</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.297101481242926</v>
+        <v>-0.2909002460366139</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.6740597669220207</v>
+        <v>-0.697856264276929</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.7025828007212169</v>
+        <v>-0.7092034407278121</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.2651556242723387</v>
+        <v>-0.3274526331220073</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.03703482098461564</v>
+        <v>-0.03284674824892875</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.2039431315540838</v>
+        <v>0.1476732152827864</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.2217737176309527</v>
+        <v>0.1722580084236114</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.500423028360494</v>
+        <v>0.4564626686058588</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.6220222613518445</v>
+        <v>0.5908879335966972</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5812959859233473</v>
+        <v>0.5433760764110858</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.7349436069102993</v>
+        <v>0.6892253091652236</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.7311230473409296</v>
+        <v>0.6786248395307837</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; -0.05161</t>
+          <t>X &gt; -0.05158</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3114</v>
+        <v>3125</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.5461542780559441</v>
+        <v>-0.5318093360548204</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.02940218757770907</v>
+        <v>-0.02370703963109122</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.5348735083532219</v>
+        <v>-0.5278953530190975</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.8355216042014817</v>
+        <v>-0.8598576447506545</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.748284059391132</v>
+        <v>-0.7569351290851927</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3054434526072711</v>
+        <v>-0.3709858337021927</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1484709793083567</v>
+        <v>-0.2224978626189653</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.1391186471831674</v>
+        <v>0.07893280410766579</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.03173971654639729</v>
+        <v>-0.02197842395495542</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.4503398633738058</v>
+        <v>0.400996064283774</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.5204255462132323</v>
+        <v>0.4845794019139191</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.6051199278845374</v>
+        <v>0.5608624220956671</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.7489612693633916</v>
+        <v>0.6956685814726882</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.7683384349954139</v>
+        <v>0.707016706443909</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; -0.04516</t>
+          <t>X &gt; -0.04513</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2956</v>
+        <v>2964</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3407070652495534</v>
+        <v>-0.2893850415760824</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.223474410454422</v>
+        <v>0.2655128402096025</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4227925640024637</v>
+        <v>-0.3792827906134377</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.4949282973112332</v>
+        <v>-0.4669441370350782</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.3065438557822802</v>
+        <v>-0.2641817555071739</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.07675268281739278</v>
+        <v>0.0607042723250899</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2282893704631448</v>
+        <v>0.2207610323078555</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.6913053193900893</v>
+        <v>0.6652451970762385</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.5478647529418481</v>
+        <v>0.5271262629225788</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.068134534247363</v>
+        <v>1.051915348999032</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>1.017920830660508</v>
+        <v>1.016352109824375</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.240697517780212</v>
+        <v>1.243096055550694</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.313435154276689</v>
+        <v>1.305729011376265</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.321973291938136</v>
+        <v>1.30437163221989</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; -0.03871</t>
+          <t>X &gt; -0.03868</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2786</v>
+        <v>2794</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.5495855584313531</v>
+        <v>-0.5101118248869838</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.04027712506012904</v>
+        <v>0.06891187595216053</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.5498656343374648</v>
+        <v>-0.555647341531234</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.4912224520948527</v>
+        <v>-0.5137392103784748</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.5447768007821452</v>
+        <v>-0.5545465045325528</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1822427712804355</v>
+        <v>0.1474235636425973</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.3839627736326108</v>
+        <v>0.3728905073212871</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.7962158479766472</v>
+        <v>0.7654268456503956</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.6119608712242908</v>
+        <v>0.5853927200615203</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>1.072372643324194</v>
+        <v>1.049117787315211</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.067432193736451</v>
+        <v>1.059569614457239</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.373450366606875</v>
+        <v>1.368094005613251</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>1.225134467443674</v>
+        <v>1.208168624392762</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.292175161521904</v>
+        <v>1.263122647746691</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; -0.03226</t>
+          <t>X &gt; -0.03223</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2575</v>
+        <v>2583</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.4112835353699467</v>
+        <v>-0.3664270044930049</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.3196625822841668</v>
+        <v>0.3502968704826657</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.7121929044043185</v>
+        <v>-0.7181826772520168</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5432530879549518</v>
+        <v>-0.5675063528891897</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.518485555350864</v>
+        <v>-0.5330457698549367</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2823741443074468</v>
+        <v>0.24264110292917</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.6624197881396583</v>
+        <v>0.6462016481331148</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.069177062228022</v>
+        <v>1.031432717537008</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.9524656498732682</v>
+        <v>0.9170906693286511</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.28756538425209</v>
+        <v>1.253803674587161</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>1.376637619796533</v>
+        <v>1.35914098333734</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.705017162381665</v>
+        <v>1.688100757452716</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.617915837023382</v>
+        <v>1.586207138546193</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.555600471149084</v>
+        <v>1.548023287938292</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; -0.02581</t>
+          <t>X &gt; -0.02579</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2381</v>
+        <v>2386</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.6802460137839361</v>
+        <v>-0.6071423560455003</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.05362651961790021</v>
+        <v>0.1326525125513029</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-1.240120261599976</v>
+        <v>-1.201133218993789</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.026107937450234</v>
+        <v>-1.007059105049059</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.019780816896997</v>
+        <v>-0.9712348971312252</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.09400293305160545</v>
+        <v>-0.07004552410199238</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.4077969716118446</v>
+        <v>0.4558086506021652</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.113748855684342</v>
+        <v>1.162996418078059</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>1.1182583553841</v>
+        <v>1.167917399221956</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.549819048950752</v>
+        <v>1.600896526827576</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.620961037877251</v>
+        <v>1.648117620975611</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.973377757601561</v>
+        <v>1.99953949030531</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>2.081440147196474</v>
+        <v>2.107104647109729</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.701855410127983</v>
+        <v>1.75204604424777</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; -0.01935</t>
+          <t>X &gt; -0.01934</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2113</v>
+        <v>2117</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.3808688384626251</v>
+        <v>-0.3648973034348373</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.4147407268029468</v>
+        <v>0.4350129767496114</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-1.065448307786909</v>
+        <v>-1.06560169779123</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.6520707338068661</v>
+        <v>-0.6744233104006554</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4824792109233158</v>
+        <v>-0.4770013509525981</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.09804724910345897</v>
+        <v>0.0792041017350158</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.5324496788887387</v>
+        <v>0.5381512246021316</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>1.150798684936831</v>
+        <v>1.158761544048737</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.494113101396209</v>
+        <v>1.499682180070188</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.899132632014478</v>
+        <v>1.904006646019496</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.005376358667398</v>
+        <v>1.983286132352085</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.587400053037406</v>
+        <v>2.561056081809568</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.526198096083064</v>
+        <v>2.496554744759194</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>2.495983398841283</v>
+        <v>2.462179672905883</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; -0.0129</t>
+          <t>X &gt; -0.01289</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1763</v>
+        <v>1768</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9263654369786707</v>
+        <v>-0.8735429761285118</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.6846078820547277</v>
+        <v>0.7344920046945944</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1.066862202530722</v>
+        <v>-1.040699214741714</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-1.106224396421162</v>
+        <v>-1.050189776306233</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-1.022693712094579</v>
+        <v>-0.9436770659680889</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.5557323449806972</v>
+        <v>-0.501208289230604</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.131680691810466</v>
+        <v>-0.05281460470041566</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.7014202517402808</v>
+        <v>0.782257612291815</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.011394409212429</v>
+        <v>1.084651518992125</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>2.230644667470571</v>
+        <v>2.297022033199767</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.455326798288304</v>
+        <v>2.488809187473628</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.146203688207748</v>
+        <v>3.169147870539881</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>3.32660655968926</v>
+        <v>3.339600803704556</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>3.47291925147168</v>
+        <v>3.475523493774226</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; -0.006451</t>
+          <t>X &gt; -0.006447</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.4094874591057831</v>
+        <v>-0.3021346169097754</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>1.479326447830388</v>
+        <v>1.573140170498867</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.513126491646787</v>
+        <v>0.5771671102016569</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.4280769361934347</v>
+        <v>-0.39568675435914</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.466366489289129</v>
+        <v>-0.4178205695233572</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.4547067453683198</v>
+        <v>-0.4307493364187067</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2462971810797896</v>
+        <v>0.2943088600701103</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.064942823007343</v>
+        <v>1.114190385401059</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.7896749521988582</v>
+        <v>0.8629320619785545</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.338612481816092</v>
+        <v>2.396246338306419</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.604869017637412</v>
+        <v>2.620677319341759</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.54037087365775</v>
+        <v>3.535986913849506</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>3.23466911613496</v>
+        <v>3.212257558714263</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>3.575017946877246</v>
+        <v>3.532730992158193</v>
       </c>
     </row>
     <row r="35">
@@ -3848,677 +3848,677 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.1871</t>
+          <t>X &lt; -0.187</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>9.423845874227553</v>
+        <v>9.394650079874921</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>3.050755019258958</v>
+        <v>3.049568232814302</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>9.798840777361072</v>
+        <v>9.79868738735675</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>6.35763734952085</v>
+        <v>6.357142857142847</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>3.438395415472783</v>
+        <v>3.486941335238555</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-3.407087697749276</v>
+        <v>-3.383130288799663</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-3.491798057015444</v>
+        <v>-3.443786378025123</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.8522856234963001</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.7420559045798072</v>
+        <v>0.8153130143595035</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>5.844518060630897</v>
+        <v>5.94386538592547</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.639816902370704</v>
+        <v>5.739724938389379</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.055147435678414</v>
+        <v>8.178844056706659</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>8.825472772841195</v>
+        <v>8.974162320619023</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.860732232591538</v>
+        <v>8.0327309921582</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.1806</t>
+          <t>X &lt; -0.1805</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7.093552054572029</v>
+        <v>6.437256596165639</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.290876599806069</v>
+        <v>1.696184774167683</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>7.215254151221245</v>
+        <v>7.618236259537198</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>6.281649507575572</v>
+        <v>6.695488721804509</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>3.615700380011788</v>
+        <v>4.100976422957842</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.533734100991424</v>
+        <v>-2.994659110854798</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-3.618444460257592</v>
+        <v>-4.107946779027628</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1698060448918426</v>
+        <v>-0.3632532236214914</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.9550058988649823</v>
+        <v>-1.452857411705665</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>3.514224240975373</v>
+        <v>2.986471902216188</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>4.37335286994923</v>
+        <v>3.834963033627474</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>6.535390596772629</v>
+        <v>7.05102450783447</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>6.11523974345922</v>
+        <v>6.655866581270644</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>6.340975393685753</v>
+        <v>6.904911443286011</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.1742</t>
+          <t>X &lt; -0.1741</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6.519083969465647</v>
+        <v>6.489888175113016</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>2.907897876401812</v>
+        <v>2.906711089957156</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>9.51312649164678</v>
+        <v>9.512973101642459</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7.643351635235142</v>
+        <v>7.642857142857139</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>4.105062082139447</v>
+        <v>4.153608001905219</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-1.597563888225466</v>
+        <v>-1.573606479275853</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.682274247491634</v>
+        <v>-3.634262568501313</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.8506571087216344</v>
+        <v>0.8999046711153511</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-2.210325047801149</v>
+        <v>-2.137067938021453</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.06024384413100137</v>
+        <v>0.03910348116357198</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.735054997608792</v>
+        <v>1.834963033627467</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>5.769433149964122</v>
+        <v>5.893129770992367</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>4.349282296650713</v>
+        <v>4.497971844428541</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>5.575017946877246</v>
+        <v>5.747016706443908</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.1677</t>
+          <t>X &lt; -0.1676</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>116</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>7.001842590155306</v>
+        <v>6.972646795802675</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>5.390656497091477</v>
+        <v>5.389469710646821</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>11.03036787095713</v>
+        <v>11.03021448095281</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9.436455083511007</v>
+        <v>9.435960591133004</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>5.449889668346344</v>
+        <v>5.498435588112116</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.5748499048779792</v>
+        <v>0.5988073138275922</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-2.096067350939911</v>
+        <v>-2.048055671949591</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>2.609277798376802</v>
+        <v>2.658525360770518</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.624118151249426</v>
+        <v>-2.55086104146973</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-1.749899016544802</v>
+        <v>-1.650551691250229</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.2304622437705177</v>
+        <v>-0.1305542077518425</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>3.252191770653781</v>
+        <v>3.375888391682025</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>2.832040917340372</v>
+        <v>2.980730465118199</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>3.919845533084143</v>
+        <v>4.091844292650805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.1613</t>
+          <t>X &lt; -0.1612</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>128</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>10.01908396946565</v>
+        <v>9.989888175113016</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>6.845397876401819</v>
+        <v>6.844211089957163</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>11.91937649164678</v>
+        <v>11.91922310164246</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9.705851635235142</v>
+        <v>9.705357142857139</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>5.261312082139447</v>
+        <v>5.309858001905219</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8711861117745343</v>
+        <v>0.8951435207241474</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.7760242474916339</v>
+        <v>-0.7280125685013132</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>3.444407108721627</v>
+        <v>3.493654671115344</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-1.304075047801149</v>
+        <v>-1.230817938021453</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1897561558689915</v>
+        <v>0.2891034811635649</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>2.328804997608799</v>
+        <v>2.428713033627474</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>5.488183149964122</v>
+        <v>5.611879770992367</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.068032296650713</v>
+        <v>5.216721844428541</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>6.075017946877246</v>
+        <v>6.247016706443908</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.1548</t>
+          <t>X &lt; -0.1547</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>141</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>9.221211629040113</v>
+        <v>9.192015834687481</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>5.482365961508201</v>
+        <v>5.481179175063545</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>10.7613534420014</v>
+        <v>10.76120005199708</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10.18235872743373</v>
+        <v>10.18186423505573</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>6.097969883557887</v>
+        <v>6.146515803323659</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.140024764256808</v>
+        <v>2.163982173206421</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.6368746886785814</v>
+        <v>0.6848863676689021</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.006685477515951</v>
+        <v>3.055933039909668</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.309615827942991</v>
+        <v>-1.236358718163295</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.6773448083512648</v>
+        <v>0.7766921336458381</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>3.309523082715181</v>
+        <v>3.409431118733856</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.890000525850652</v>
+        <v>7.013697146878897</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>6.469849672537244</v>
+        <v>6.618539220315071</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>6.695585322763776</v>
+        <v>6.867584082330438</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.1484</t>
+          <t>X &lt; -0.1483</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>159</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>10.41216573047193</v>
+        <v>10.3829699361193</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.285256366967857</v>
+        <v>6.284069580523202</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>9.66406988787319</v>
+        <v>9.663916497868868</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.794295031461552</v>
+        <v>9.793800539083549</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>7.369213025535672</v>
+        <v>7.417758945301443</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.521932967120442</v>
+        <v>4.545890376070055</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.17936097263415</v>
+        <v>3.227372651624471</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.599084781677597</v>
+        <v>4.648332344071314</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.1355869018843876</v>
+        <v>0.208844011664084</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1.172460558384714</v>
+        <v>1.271807883679287</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.112413488174838</v>
+        <v>4.212321524193513</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>6.033584093360346</v>
+        <v>6.157280714388591</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>5.613433240046938</v>
+        <v>5.762122787824765</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>5.83916889027347</v>
+        <v>6.011167649840132</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.1419</t>
+          <t>X &lt; -0.1418</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>9.681246131627809</v>
+        <v>9.85547957296248</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5.907897876401819</v>
+        <v>6.121764853398027</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.296910275430569</v>
+        <v>9.491467725298371</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9.427135419018931</v>
+        <v>9.621351766513051</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>5.645602622679995</v>
+        <v>5.906296173948235</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.240273949612373</v>
+        <v>2.953275241154259</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.074482509265124</v>
+        <v>2.354984743326646</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.147954406018926</v>
+        <v>2.426786391545456</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.07518991266601205</v>
+        <v>0.2392761480000516</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9251087089958716</v>
+        <v>-0.584552432814931</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.4918117543655569</v>
+        <v>0.8242103454554339</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>2.147811528342501</v>
+        <v>2.495280308626782</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.727660675029092</v>
+        <v>2.100122382062956</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.8723152441745441</v>
+        <v>1.27389842687402</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.1355</t>
+          <t>X &lt; -0.1354</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>208</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>8.576776277157961</v>
+        <v>8.54758048280533</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>4.080974799478746</v>
+        <v>4.07978801303409</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>7.532357260877554</v>
+        <v>7.532203870873232</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9.104890096773602</v>
+        <v>9.104395604395599</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>6.643523620600988</v>
+        <v>6.692069540366759</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>3.575513034851461</v>
+        <v>3.599470443801074</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.529264214046826</v>
+        <v>2.577275893037147</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.504503262567781</v>
+        <v>3.553750824961497</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.039674952198851</v>
+        <v>1.112932061978547</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.1897561558689915</v>
+        <v>0.2891034811635649</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>1.908131920685726</v>
+        <v>2.008039956704401</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.942510073041049</v>
+        <v>2.066206694069294</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.52235921972764</v>
+        <v>1.671048767505468</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.3057871776464722</v>
+        <v>0.4777859372131346</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.129</t>
+          <t>X &lt; -0.1289</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>6.440245795191792</v>
+        <v>6.167574125526244</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.339433146111361</v>
+        <v>2.105058197395181</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.679101595381219</v>
+        <v>5.430328473543284</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7.469077776313981</v>
+        <v>7.213105076741428</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>5.685974945209985</v>
+        <v>5.484186514301911</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.419033622147978</v>
+        <v>1.624740628162165</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.9193855035457119</v>
+        <v>1.150861398440838</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>1.282192378431169</v>
+        <v>1.511474919049228</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.02360305609990121</v>
+        <v>-0.178390252071047</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.04364633375756455</v>
+        <v>0.2374505886015825</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.9964657859905373</v>
+        <v>1.27297956255309</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.2139693396624338</v>
+        <v>0.09147687843038455</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.6341201929758427</v>
+        <v>-0.7169041886293073</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-2.06813558009371</v>
+        <v>-1.707528748101552</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.1226</t>
+          <t>X &lt; -0.1225</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>4.500216044937346</v>
+        <v>4.632745317970155</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.756954480175402</v>
+        <v>1.545808834318059</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>5.51312649164678</v>
+        <v>5.287409191868029</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7.530144088065327</v>
+        <v>7.296992481202999</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>5.482420572705486</v>
+        <v>5.303983941754844</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2.383568187246233</v>
+        <v>2.193310813957233</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>1.544140846847988</v>
+        <v>1.380775025483651</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.077072203061249</v>
+        <v>0.9149422651003078</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.62541938742379</v>
+        <v>-1.753609291404906</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.720621202621572</v>
+        <v>-1.825558172971775</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4158883986176178</v>
+        <v>-0.1499993723875619</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.890944208526442</v>
+        <v>-1.595592033518912</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-3.443170533537966</v>
+        <v>-3.118569508954913</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-4.349510355009549</v>
+        <v>-3.997344195811728</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.1161</t>
+          <t>X &lt; -0.116</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>304</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.42697870630775</v>
+        <v>4.397782911955119</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.8421084027176065</v>
+        <v>0.8409216162729507</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.407863333752047</v>
+        <v>3.407709943747726</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.182825319445676</v>
+        <v>5.182330827067673</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>2.999798924244715</v>
+        <v>3.048344844010487</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.323488743353487</v>
+        <v>1.3474461523031</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.5808836472452157</v>
+        <v>0.6288953262355363</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.7717097403005795</v>
+        <v>0.8209573026942962</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-2.578746100432731</v>
+        <v>-2.505488990653035</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-3.099717528341543</v>
+        <v>-3.00037020304697</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-1.988629212917516</v>
+        <v>-1.888721176898841</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-3.927935271088508</v>
+        <v>-3.804238650060263</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-4.677033492822972</v>
+        <v>-4.528343945045144</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.438139947859604</v>
+        <v>-5.266141188292941</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.1097</t>
+          <t>X &lt; -0.1096</t>
         </is>
       </c>
       <c r="B18" t="n">
         <v>352</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.348629424011108</v>
+        <v>2.319433629658477</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.021534240038186</v>
+        <v>1.02034745359353</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>2.3313083098286</v>
+        <v>2.331154919824279</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.313806180689681</v>
+        <v>3.313311688311678</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.775516627593987</v>
+        <v>2.824062547359759</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.368345202683628</v>
+        <v>1.392302611633241</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.431362116144733</v>
+        <v>0.4793737951350536</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.03570652764200588</v>
+        <v>0.01354103475171087</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.233052320528422</v>
+        <v>-1.159795210748726</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.367062025949188</v>
+        <v>-2.267714700654615</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.719490456936661</v>
+        <v>-1.619582420917986</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-3.105566850035878</v>
+        <v>-2.981870229007633</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.093899521531107</v>
+        <v>-3.945209973753279</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.720436598577294</v>
+        <v>-4.548437839010631</v>
       </c>
     </row>
     <row r="19">
@@ -4531,826 +4531,826 @@
         <v>396</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.317063767445447</v>
+        <v>2.287867973092816</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.210928179432116</v>
+        <v>1.209741392987461</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.956482948366457</v>
+        <v>1.955988455988454</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.165668142745503</v>
+        <v>1.214214062511275</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.05210934277092605</v>
+        <v>-0.02815193382131298</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.399445964663343</v>
+        <v>-1.351434285673022</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.361464103399591</v>
+        <v>-1.312216541005874</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.927496764972858</v>
+        <v>-1.854239655193162</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.524890308777472</v>
+        <v>-2.425542983482899</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.224540961987159</v>
+        <v>-2.124632925968484</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-3.200263819732847</v>
+        <v>-3.076567198704602</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-4.125465178096754</v>
+        <v>-3.976775630318926</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-4.657305285445993</v>
+        <v>-4.485306525879331</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.09677</t>
+          <t>X &lt; -0.0967</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>441</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.394367416177666</v>
+        <v>2.365171621825034</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1029092142702979</v>
+        <v>0.1017224278256421</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.068682047202337</v>
+        <v>1.068528657198016</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.879179299634238</v>
+        <v>1.878684807256235</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6606176376950046</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4025525503569867</v>
+        <v>-0.3785951414073736</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.167535018466694</v>
+        <v>-1.119523339476373</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-1.181088923024404</v>
+        <v>-1.131841360630688</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.468828449161691</v>
+        <v>-1.395571339381995</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-2.318747245491551</v>
+        <v>-2.219399920196977</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-2.296691034137233</v>
+        <v>-2.196782998118557</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.622857099468987</v>
+        <v>-3.499160478440743</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-4.723280061625935</v>
+        <v>-4.574590513848108</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-5.404573889857446</v>
+        <v>-5.232575130290783</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; -0.09032</t>
+          <t>X &lt; -0.09026</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2.028102005537789</v>
+        <v>2.089888175113018</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.1842864923356586</v>
+        <v>-0.0932889100428369</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.8237477341317501</v>
+        <v>0.9129731016424643</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.354774480926523</v>
+        <v>1.442857142857143</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.016885729434037</v>
+        <v>1.153608001905226</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1118549494498851</v>
+        <v>0.2263935207241516</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.5740578146259026</v>
+        <v>-0.4342625685013104</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.8407256568094326</v>
+        <v>-0.7000953288846503</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.302509416538626</v>
+        <v>-1.137067938021453</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-2.553229816074897</v>
+        <v>-2.360896518836434</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-2.757930974335089</v>
+        <v>-2.565036966372524</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.324755226789385</v>
+        <v>-3.106870229007633</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.145707683309212</v>
+        <v>-3.902028155571458</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-4.921976041098709</v>
+        <v>-4.65298329355609</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; -0.08387</t>
+          <t>X &lt; -0.08381</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>567</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.721905838954186</v>
+        <v>2.692710044601554</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.5816192167898251</v>
+        <v>0.5804324303451693</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>2.126883105403394</v>
+        <v>2.126729715399073</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>2.609841935058775</v>
+        <v>2.609347442680772</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>2.07155238196308</v>
+        <v>2.120098301728852</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.7816248242965784</v>
+        <v>0.8055822332461915</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.00855290710362766</v>
+        <v>0.039458771886693</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.6519883939238724</v>
+        <v>-0.6027408315301557</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8893373934801616</v>
+        <v>-0.8160802837004653</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.268356718910546</v>
+        <v>-2.169009393615973</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.473057877170739</v>
+        <v>-2.373149841152063</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-2.967780253915954</v>
+        <v>-2.84408363288771</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-3.740664793296382</v>
+        <v>-3.591975245518555</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-4.220396515203888</v>
+        <v>-4.048397755637225</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; -0.07742</t>
+          <t>X &lt; -0.07736</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>639</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.509694298104144</v>
+        <v>1.480498503751512</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.7274698857264994</v>
+        <v>-0.7286566721711552</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.5991984791272174</v>
+        <v>0.599045089122896</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.8859181454072811</v>
+        <v>0.8854236530292781</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.756079296536939</v>
+        <v>1.804625216302711</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.1374699915118498</v>
+        <v>-0.1135125825622367</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.6916639188531377</v>
+        <v>-0.6436522398628171</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-1.002238039948168</v>
+        <v>-0.9529904775544509</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.219714719162653</v>
+        <v>-1.146457609382956</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-2.382622560875923</v>
+        <v>-2.28327523558135</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-3.213301809902937</v>
+        <v>-3.113393773884262</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-3.178923657547614</v>
+        <v>-3.055227036519369</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-3.912063556244441</v>
+        <v>-3.763374008466613</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-4.31230599678473</v>
+        <v>-4.140307237218067</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; -0.07096</t>
+          <t>X &lt; -0.07092</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.055838477093943</v>
+        <v>1.026642682741311</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.4166513607687818</v>
+        <v>-0.4178381472134376</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2981472960850553</v>
+        <v>0.297993906080734</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1.537942481282293</v>
+        <v>1.53744798890429</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.247919224996586</v>
+        <v>2.296465144762358</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.08993559418940578</v>
+        <v>-0.06597818523979271</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.174645953455574</v>
+        <v>-0.1266342744652533</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.5030183420412015</v>
+        <v>-0.4537707796474848</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.702696753765089</v>
+        <v>-0.6294396439853926</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.69131180529606</v>
+        <v>-1.591964480001486</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-2.312101729159579</v>
+        <v>-2.212193693140904</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-2.277723576804256</v>
+        <v>-2.154026955776011</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-2.836570685318776</v>
+        <v>-2.687881137540948</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.443012566298897</v>
+        <v>-3.271013806732235</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; -0.06451</t>
+          <t>X &lt; -0.06447</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>826</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.393175979150875</v>
+        <v>1.410274182350648</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.234774389719007</v>
+        <v>1.153996976567541</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.7189376296613048</v>
+        <v>0.7602589882528363</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1.575555025065647</v>
+        <v>1.613906600034461</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>2.732180726207247</v>
+        <v>2.692811861977596</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.9714433756970564</v>
+        <v>1.156188454379155</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.523536890522891</v>
+        <v>0.7336505798702149</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.06459712856651123</v>
+        <v>0.09314138609119027</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.1165514655160393</v>
+        <v>0.2977146706742033</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.217628832024474</v>
+        <v>-1.063677655474883</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.301264614982003</v>
+        <v>-1.201356578963328</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.509017213231999</v>
+        <v>-1.385320592203755</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-2.171298817150735</v>
+        <v>-2.022609269372907</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-2.3087592928322</v>
+        <v>-2.136760533265537</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; -0.05806</t>
+          <t>X &lt; -0.05802</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>938</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.463646869252436</v>
+        <v>1.417701338594966</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.4921196248026689</v>
+        <v>0.4714669285983533</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.9502267048663953</v>
+        <v>0.9269858404959592</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.359769545682902</v>
+        <v>2.436912344555651</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>2.461138841201283</v>
+        <v>2.478448766236426</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>1.052755941198846</v>
+        <v>1.265034709683803</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1151671171139128</v>
+        <v>0.3551217202460322</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4585113347751815</v>
+        <v>-0.2648137135817876</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.4128836831956022</v>
+        <v>-0.2434509167448553</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.369412287627817</v>
+        <v>-1.221812386781053</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.787333062092692</v>
+        <v>-1.687425026074017</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-1.646345101635028</v>
+        <v>-1.522648480606783</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-2.173105763050778</v>
+        <v>-2.02441621527295</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-2.160589729028942</v>
+        <v>-1.98859096946228</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; -0.05161</t>
+          <t>X &lt; -0.05158</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>1059</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.532303988351394</v>
+        <v>1.488006707568339</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2044040142677233</v>
+        <v>0.1870497541152076</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.509349343393716</v>
+        <v>1.486632556016872</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.489432843922579</v>
+        <v>2.557250369573978</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.234429409807063</v>
+        <v>2.25614798309055</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.020944138214574</v>
+        <v>1.21190622063007</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6529476599682269</v>
+        <v>0.8690299997018869</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.1918358091253936</v>
+        <v>-0.01534956617279448</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2193255659854501</v>
+        <v>0.3765984144761987</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-1.008308055651305</v>
+        <v>-0.866556896194929</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-1.213009213911498</v>
+        <v>-1.113101177892823</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.461917180536354</v>
+        <v>-1.338220559508109</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.882068033849762</v>
+        <v>-1.733378486071935</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.939618502603395</v>
+        <v>-1.767619743036732</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; -0.04516</t>
+          <t>X &lt; -0.04513</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7594449210653238</v>
+        <v>0.6327453179701621</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.4415688996441247</v>
+        <v>-0.5422685018795761</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.9684177139601573</v>
+        <v>0.8599118771526619</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1.226274459537279</v>
+        <v>1.15306122448979</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.7700867126813193</v>
+        <v>0.66381208353787</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.08196454503991646</v>
+        <v>-0.04299423437789329</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.3683876410824354</v>
+        <v>-0.3485482827870285</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.492810434417237</v>
+        <v>-1.423624740649366</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.060776978778961</v>
+        <v>-1.007877422894715</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.321542118576367</v>
+        <v>-2.278408793795521</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-2.197566202062518</v>
+        <v>-2.192882994218557</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-2.738372930561759</v>
+        <v>-2.746214491302716</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.912015977794645</v>
+        <v>-2.895470778522281</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.932788133648636</v>
+        <v>-2.892327555851175</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; -0.03871</t>
+          <t>X &lt; -0.03868</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1387</v>
+        <v>1390</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.044263825580764</v>
+        <v>0.9616133003814511</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.008617300862248101</v>
+        <v>-0.04890809400848184</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.052694836970524</v>
+        <v>1.060575105937374</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1.006922549561999</v>
+        <v>1.047295224460576</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.116581160613173</v>
+        <v>1.130701774274591</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.2747973176202834</v>
+        <v>-0.2039789721125302</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.6087342330720276</v>
+        <v>-0.5840833570317869</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.436293143621555</v>
+        <v>-1.369822732041037</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9925889266764187</v>
+        <v>-0.9374986630752957</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.914605776358833</v>
+        <v>-1.866068932629538</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.903012774561354</v>
+        <v>-1.887538763640684</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.51751710237906</v>
+        <v>-2.509747926849357</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.216687422166878</v>
+        <v>-2.185481392981536</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-2.351442038703148</v>
+        <v>-2.296148761181996</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; -0.03226</t>
+          <t>X &lt; -0.03223</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.6109015834569007</v>
+        <v>0.5371518567050515</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.438135852517604</v>
+        <v>-0.4863237359134871</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.103382581590573</v>
+        <v>1.109988027015589</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.8933516352351418</v>
+        <v>0.9289267945984392</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.8550620821394475</v>
+        <v>0.8750010367310921</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.3761755204956359</v>
+        <v>-0.311005359176292</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.9275808807832533</v>
+        <v>-0.8982725311414086</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.582384192905401</v>
+        <v>-1.517540811750706</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.330475235535815</v>
+        <v>-1.271731279667343</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-1.867502917973304</v>
+        <v>-1.812424903115904</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-2.009625853455034</v>
+        <v>-1.982764806572277</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-2.538451706105967</v>
+        <v>-2.515364919825871</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.39539855441312</v>
+        <v>-2.34837418930038</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-2.294819349743527</v>
+        <v>-2.286712212981449</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; -0.02581</t>
+          <t>X &lt; -0.02579</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1792</v>
+        <v>1798</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.856125126306587</v>
+        <v>0.7567763257221003</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.001951873180821906</v>
+        <v>-0.1065779465876844</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.606615640227744</v>
+        <v>1.548410532428733</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1.37831822766276</v>
+        <v>1.346068660022148</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>1.37247155289154</v>
+        <v>1.299787403898577</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.1961930794445479</v>
+        <v>0.163235625987312</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.4156819440895134</v>
+        <v>-0.4768346305855644</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-1.354700034135512</v>
+        <v>-1.411798046577395</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-1.304075047801149</v>
+        <v>-1.363483032361074</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-1.874975986988147</v>
+        <v>-1.935355152928608</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-1.968070002391201</v>
+        <v>-1.998370299705861</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-2.435923992893017</v>
+        <v>-2.465958611442318</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-2.577056989063578</v>
+        <v>-2.608813472590363</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-2.072303481694185</v>
+        <v>-2.137299200118939</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; -0.01935</t>
+          <t>X &lt; -0.01934</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2060</v>
+        <v>2067</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.3492726487109294</v>
+        <v>0.3318920286775651</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.3650934111102799</v>
+        <v>-0.3842330333569066</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.057920680508772</v>
+        <v>1.052472138251325</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.6821113251576207</v>
+        <v>0.7006606110652243</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.5098124456876718</v>
+        <v>0.5004288111537747</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.03888299588792421</v>
+        <v>-0.01938961180596976</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.4367623600583528</v>
+        <v>-0.4394698973344902</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-1.071672988365755</v>
+        <v>-1.072116554162029</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-1.375373591490472</v>
+        <v>-1.372589173542693</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-1.788399183936832</v>
+        <v>-1.784170299618658</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-1.896012963556252</v>
+        <v>-1.865520058159959</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-2.492702772365973</v>
+        <v>-2.457764380771764</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-2.4274167324755</v>
+        <v>-2.391776704894475</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-2.395855839530519</v>
+        <v>-2.35845015373993</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; -0.0129</t>
+          <t>X &lt; -0.01289</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2410</v>
+        <v>2416</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.642791044351867</v>
+        <v>0.6032902369686894</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.4497180176379203</v>
+        <v>-0.4850414873624231</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.7512217297420207</v>
+        <v>0.729467947003279</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.8214792242989404</v>
+        <v>0.7768777614138429</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.7619207642778676</v>
+        <v>0.6999997544825405</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.4604792295191515</v>
+        <v>0.4181426956416416</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.1912222270002815</v>
+        <v>0.1325554257207244</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.419052434846833</v>
+        <v>-0.4758178722372577</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.6045159191704457</v>
+        <v>-0.6554487723874232</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-1.495928491433915</v>
+        <v>-1.53940891553065</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-1.659135873760498</v>
+        <v>-1.679712452110437</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-2.164176808542102</v>
+        <v>-2.178003396914995</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-2.293871230320242</v>
+        <v>-2.302607386022437</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.400085787562588</v>
+        <v>-2.403645545211717</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; -0.006451</t>
+          <t>X &lt; -0.006447</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2778</v>
+        <v>2784</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1752218014828699</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6989243857166798</v>
+        <v>-0.745634058628589</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2842873014566649</v>
+        <v>-0.3158847572905898</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2247386276893266</v>
+        <v>0.2078410311493002</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.2452489980272929</v>
+        <v>0.219845023029464</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2747841880061017</v>
+        <v>0.2616370737327429</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.04198647770746788</v>
+        <v>-0.06600746280442849</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.4534091021455922</v>
+        <v>-0.4764394149061602</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.2787195762388777</v>
+        <v>-0.3145509068274777</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-1.056644132107962</v>
+        <v>-1.082847738348626</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-1.189351049907401</v>
+        <v>-1.195535710541883</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.658932580777417</v>
+        <v>-1.656044672654431</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-1.503129510404726</v>
+        <v>-1.49305149488923</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-1.673362182712395</v>
+        <v>-1.655282144130801</v>
       </c>
     </row>
     <row r="35">
@@ -5360,49 +5360,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3158</v>
+        <v>3165</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.1916833181882822</v>
+        <v>-0.2266472579578434</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.5861008601743052</v>
+        <v>-0.6129739494129112</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.5216286426344254</v>
+        <v>-0.5342709928457339</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.247925229493049</v>
+        <v>-0.2469066366704169</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.3374364103089107</v>
+        <v>0.3205897284332622</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.1146435754051467</v>
+        <v>0.1065069780200787</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-0.07930050500507235</v>
+        <v>-0.09453999599185892</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.4341530178606448</v>
+        <v>-0.4485658429180788</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.09794771320159157</v>
+        <v>-0.121295067358993</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.4413771141531626</v>
+        <v>-0.4544276011968051</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.7093894468356439</v>
+        <v>-0.7041783805139374</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.9599115793806092</v>
+        <v>-0.9442557673720131</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.9825733081624648</v>
+        <v>-0.9745486862094879</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-1.231821825130353</v>
+        <v>-1.213488822782004</v>
       </c>
     </row>
   </sheetData>
